--- a/data/plan_justicia/procedimientos_personas_plan_justicia.xlsx
+++ b/data/plan_justicia/procedimientos_personas_plan_justicia.xlsx
@@ -1,29 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://serviciossaludimssbienestar.sharepoint.com/sites/DivisindeProcesamientodeinformacin/Comando Florence Nightingale/Proyectos/62_Planes de justicia/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_28DA2E70065D6D85F1CCAC87A19DAC72BC14AAAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E179290C-222C-47BE-9B4D-6AF716F44CE4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$464</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="46">
   <si>
     <t>anio_insert</t>
   </si>
@@ -166,12 +157,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,6 +167,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -187,21 +175,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -209,42 +191,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Millares" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -282,7 +265,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -316,7 +299,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -351,10 +333,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -527,36 +508,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:E464"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="77.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E463"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -567,13 +540,13 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>163062</v>
+        <v>174617</v>
       </c>
       <c r="E2">
-        <v>70543</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>73819</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -584,13 +557,13 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>848241</v>
+        <v>908482</v>
       </c>
       <c r="E3">
-        <v>325237</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>339689</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -601,13 +574,13 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>52552</v>
+        <v>54742</v>
       </c>
       <c r="E4">
-        <v>15900</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>16439</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -618,13 +591,13 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>5684</v>
+        <v>5819</v>
       </c>
       <c r="E5">
-        <v>2825</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -641,7 +614,7 @@
         <v>5976</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -652,13 +625,13 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>9905</v>
+        <v>9936</v>
       </c>
       <c r="E7">
-        <v>4939</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -669,13 +642,13 @@
         <v>41</v>
       </c>
       <c r="D8">
-        <v>34150</v>
+        <v>37240</v>
       </c>
       <c r="E8">
-        <v>13708</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>14666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -686,13 +659,13 @@
         <v>41</v>
       </c>
       <c r="D9">
-        <v>46066</v>
+        <v>46342</v>
       </c>
       <c r="E9">
-        <v>21442</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>21494</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -703,13 +676,13 @@
         <v>41</v>
       </c>
       <c r="D10">
-        <v>161075</v>
+        <v>171603</v>
       </c>
       <c r="E10">
-        <v>61643</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>64063</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -720,13 +693,13 @@
         <v>41</v>
       </c>
       <c r="D11">
-        <v>3083</v>
+        <v>3331</v>
       </c>
       <c r="E11">
-        <v>1573</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -737,13 +710,13 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>12645</v>
+        <v>13252</v>
       </c>
       <c r="E12">
-        <v>6176</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6411</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -754,13 +727,13 @@
         <v>41</v>
       </c>
       <c r="D13">
-        <v>122910</v>
+        <v>131940</v>
       </c>
       <c r="E13">
-        <v>48057</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>50300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -771,13 +744,13 @@
         <v>41</v>
       </c>
       <c r="D14">
-        <v>208179</v>
+        <v>226523</v>
       </c>
       <c r="E14">
-        <v>82101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>86238</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -788,13 +761,13 @@
         <v>41</v>
       </c>
       <c r="D15">
-        <v>147572</v>
+        <v>157207</v>
       </c>
       <c r="E15">
-        <v>63555</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>66334</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -805,13 +778,13 @@
         <v>41</v>
       </c>
       <c r="D16">
-        <v>232473</v>
+        <v>246360</v>
       </c>
       <c r="E16">
-        <v>85705</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>89424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -822,13 +795,13 @@
         <v>41</v>
       </c>
       <c r="D17">
-        <v>197686</v>
+        <v>208572</v>
       </c>
       <c r="E17">
-        <v>88599</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>91483</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -839,13 +812,13 @@
         <v>41</v>
       </c>
       <c r="D18">
-        <v>39263</v>
+        <v>42626</v>
       </c>
       <c r="E18">
-        <v>19153</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>20084</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -856,13 +829,13 @@
         <v>41</v>
       </c>
       <c r="D19">
-        <v>22477</v>
+        <v>24630</v>
       </c>
       <c r="E19">
-        <v>9394</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>9928</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -873,13 +846,13 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>18811</v>
+        <v>19542</v>
       </c>
       <c r="E20">
-        <v>9396</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>9635</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -890,13 +863,13 @@
         <v>41</v>
       </c>
       <c r="D21">
-        <v>327235</v>
+        <v>346336</v>
       </c>
       <c r="E21">
-        <v>123162</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>127258</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -907,13 +880,13 @@
         <v>41</v>
       </c>
       <c r="D22">
-        <v>11548</v>
+        <v>11877</v>
       </c>
       <c r="E22">
-        <v>5252</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>5355</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -924,13 +897,13 @@
         <v>41</v>
       </c>
       <c r="D23">
-        <v>115952</v>
+        <v>124722</v>
       </c>
       <c r="E23">
-        <v>46005</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>48162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -941,13 +914,13 @@
         <v>41</v>
       </c>
       <c r="D24">
-        <v>183462</v>
+        <v>200167</v>
       </c>
       <c r="E24">
-        <v>73318</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>77455</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -958,13 +931,13 @@
         <v>41</v>
       </c>
       <c r="D25">
-        <v>308260</v>
+        <v>325636</v>
       </c>
       <c r="E25">
-        <v>112442</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+        <v>117163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -974,14 +947,14 @@
       <c r="C26" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="1">
-        <v>197195</v>
-      </c>
-      <c r="E26" s="1">
-        <v>76699</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D26">
+        <v>197233</v>
+      </c>
+      <c r="E26">
+        <v>76706</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -992,13 +965,13 @@
         <v>41</v>
       </c>
       <c r="D27">
-        <v>103962</v>
+        <v>111267</v>
       </c>
       <c r="E27">
-        <v>30392</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>31619</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -1009,13 +982,13 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>179918</v>
+        <v>191694</v>
       </c>
       <c r="E28">
-        <v>68397</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>71200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -1026,13 +999,13 @@
         <v>41</v>
       </c>
       <c r="D29">
-        <v>16686</v>
+        <v>18006</v>
       </c>
       <c r="E29">
-        <v>8165</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>8528</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -1043,13 +1016,13 @@
         <v>41</v>
       </c>
       <c r="D30">
-        <v>2463</v>
+        <v>2509</v>
       </c>
       <c r="E30">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -1060,13 +1033,13 @@
         <v>41</v>
       </c>
       <c r="D31">
-        <v>7729</v>
+        <v>8256</v>
       </c>
       <c r="E31">
-        <v>3413</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3577</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -1077,13 +1050,13 @@
         <v>41</v>
       </c>
       <c r="D32">
-        <v>279244</v>
+        <v>303152</v>
       </c>
       <c r="E32">
-        <v>80634</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>84901</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -1094,13 +1067,13 @@
         <v>42</v>
       </c>
       <c r="D33">
-        <v>1556</v>
+        <v>1594</v>
       </c>
       <c r="E33">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1111,13 +1084,13 @@
         <v>42</v>
       </c>
       <c r="D34">
-        <v>34416</v>
+        <v>36854</v>
       </c>
       <c r="E34">
-        <v>25453</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>27223</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -1128,13 +1101,13 @@
         <v>42</v>
       </c>
       <c r="D35">
-        <v>1355</v>
+        <v>1475</v>
       </c>
       <c r="E35">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1145,13 +1118,13 @@
         <v>42</v>
       </c>
       <c r="D36">
-        <v>1821</v>
+        <v>2079</v>
       </c>
       <c r="E36">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -1162,13 +1135,13 @@
         <v>42</v>
       </c>
       <c r="D37">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="E37">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -1179,13 +1152,13 @@
         <v>42</v>
       </c>
       <c r="D38">
-        <v>2464</v>
+        <v>2639</v>
       </c>
       <c r="E38">
-        <v>2074</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -1196,13 +1169,13 @@
         <v>42</v>
       </c>
       <c r="D39">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E39">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -1219,7 +1192,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -1230,13 +1203,13 @@
         <v>42</v>
       </c>
       <c r="D41">
-        <v>5367</v>
+        <v>5766</v>
       </c>
       <c r="E41">
-        <v>4510</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4836</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -1247,13 +1220,13 @@
         <v>42</v>
       </c>
       <c r="D42">
-        <v>10991</v>
+        <v>12333</v>
       </c>
       <c r="E42">
-        <v>8217</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>9202</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -1264,13 +1237,13 @@
         <v>42</v>
       </c>
       <c r="D43">
-        <v>1512</v>
+        <v>1660</v>
       </c>
       <c r="E43">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -1281,13 +1254,13 @@
         <v>42</v>
       </c>
       <c r="D44">
-        <v>7308</v>
+        <v>7790</v>
       </c>
       <c r="E44">
-        <v>6134</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6520</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -1304,7 +1277,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -1315,13 +1288,13 @@
         <v>42</v>
       </c>
       <c r="D46">
-        <v>2892</v>
+        <v>3025</v>
       </c>
       <c r="E46">
-        <v>2579</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -1338,7 +1311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -1349,13 +1322,13 @@
         <v>42</v>
       </c>
       <c r="D48">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="E48">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -1366,13 +1339,13 @@
         <v>42</v>
       </c>
       <c r="D49">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="E49">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -1383,13 +1356,13 @@
         <v>42</v>
       </c>
       <c r="D50">
-        <v>18312</v>
+        <v>19645</v>
       </c>
       <c r="E50">
-        <v>8969</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>9784</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -1406,7 +1379,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -1417,13 +1390,13 @@
         <v>42</v>
       </c>
       <c r="D52">
-        <v>1883</v>
+        <v>2064</v>
       </c>
       <c r="E52">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -1434,13 +1407,13 @@
         <v>42</v>
       </c>
       <c r="D53">
-        <v>8115</v>
+        <v>8824</v>
       </c>
       <c r="E53">
-        <v>6173</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6662</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -1451,13 +1424,13 @@
         <v>42</v>
       </c>
       <c r="D54">
-        <v>8136</v>
+        <v>8571</v>
       </c>
       <c r="E54">
-        <v>6503</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6853</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -1467,14 +1440,14 @@
       <c r="C55" t="s">
         <v>42</v>
       </c>
-      <c r="D55" s="1">
-        <v>5998</v>
-      </c>
-      <c r="E55" s="1">
-        <v>5174</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D55">
+        <v>5999</v>
+      </c>
+      <c r="E55">
+        <v>5175</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -1485,13 +1458,13 @@
         <v>42</v>
       </c>
       <c r="D56">
-        <v>25295</v>
+        <v>26966</v>
       </c>
       <c r="E56">
-        <v>8140</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>8508</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -1502,13 +1475,13 @@
         <v>42</v>
       </c>
       <c r="D57">
-        <v>2131</v>
+        <v>2269</v>
       </c>
       <c r="E57">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -1519,13 +1492,13 @@
         <v>42</v>
       </c>
       <c r="D58">
-        <v>633</v>
+        <v>742</v>
       </c>
       <c r="E58">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -1536,13 +1509,13 @@
         <v>42</v>
       </c>
       <c r="D59">
-        <v>4196</v>
+        <v>4466</v>
       </c>
       <c r="E59">
-        <v>2999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -1553,13 +1526,13 @@
         <v>42</v>
       </c>
       <c r="D60">
-        <v>2622</v>
+        <v>2887</v>
       </c>
       <c r="E60">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -1570,13 +1543,13 @@
         <v>42</v>
       </c>
       <c r="D61">
-        <v>4913</v>
+        <v>5553</v>
       </c>
       <c r="E61">
-        <v>3482</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3922</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -1587,13 +1560,13 @@
         <v>43</v>
       </c>
       <c r="D62">
-        <v>5489</v>
+        <v>5854</v>
       </c>
       <c r="E62">
-        <v>2738</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -1604,13 +1577,13 @@
         <v>43</v>
       </c>
       <c r="D63">
-        <v>85309</v>
+        <v>92414</v>
       </c>
       <c r="E63">
-        <v>39957</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>42226</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -1621,13 +1594,13 @@
         <v>43</v>
       </c>
       <c r="D64">
-        <v>1304</v>
+        <v>1351</v>
       </c>
       <c r="E64">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -1638,13 +1611,13 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>1852</v>
+        <v>2116</v>
       </c>
       <c r="E65">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -1655,13 +1628,13 @@
         <v>43</v>
       </c>
       <c r="D66">
-        <v>597</v>
+        <v>620</v>
       </c>
       <c r="E66">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -1672,13 +1645,13 @@
         <v>43</v>
       </c>
       <c r="D67">
-        <v>3430</v>
+        <v>3727</v>
       </c>
       <c r="E67">
-        <v>1579</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -1695,7 +1668,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -1712,7 +1685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -1723,13 +1696,13 @@
         <v>43</v>
       </c>
       <c r="D70">
-        <v>11519</v>
+        <v>12352</v>
       </c>
       <c r="E70">
-        <v>5728</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6008</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>5</v>
       </c>
@@ -1740,13 +1713,13 @@
         <v>43</v>
       </c>
       <c r="D71">
-        <v>21158</v>
+        <v>22831</v>
       </c>
       <c r="E71">
-        <v>10388</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>11097</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>5</v>
       </c>
@@ -1757,13 +1730,13 @@
         <v>43</v>
       </c>
       <c r="D72">
-        <v>1703</v>
+        <v>1849</v>
       </c>
       <c r="E72">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>5</v>
       </c>
@@ -1774,13 +1747,13 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>8921</v>
+        <v>9689</v>
       </c>
       <c r="E73">
-        <v>4590</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4908</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>5</v>
       </c>
@@ -1791,13 +1764,13 @@
         <v>43</v>
       </c>
       <c r="D74">
-        <v>8451</v>
+        <v>8967</v>
       </c>
       <c r="E74">
-        <v>4439</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4601</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -1808,13 +1781,13 @@
         <v>43</v>
       </c>
       <c r="D75">
-        <v>1504</v>
+        <v>1588</v>
       </c>
       <c r="E75">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -1825,13 +1798,13 @@
         <v>43</v>
       </c>
       <c r="D76">
-        <v>1187</v>
+        <v>1217</v>
       </c>
       <c r="E76">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -1842,13 +1815,13 @@
         <v>43</v>
       </c>
       <c r="D77">
-        <v>51331</v>
+        <v>56403</v>
       </c>
       <c r="E77">
-        <v>20729</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>21501</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -1865,7 +1838,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>5</v>
       </c>
@@ -1876,13 +1849,13 @@
         <v>43</v>
       </c>
       <c r="D79">
-        <v>2564</v>
+        <v>2865</v>
       </c>
       <c r="E79">
-        <v>1417</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>5</v>
       </c>
@@ -1893,13 +1866,13 @@
         <v>43</v>
       </c>
       <c r="D80">
-        <v>39879</v>
+        <v>43659</v>
       </c>
       <c r="E80">
-        <v>19140</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>20414</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>5</v>
       </c>
@@ -1910,13 +1883,13 @@
         <v>43</v>
       </c>
       <c r="D81">
-        <v>21340</v>
+        <v>22328</v>
       </c>
       <c r="E81">
-        <v>9247</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+        <v>9489</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>5</v>
       </c>
@@ -1926,14 +1899,14 @@
       <c r="C82" t="s">
         <v>43</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D82">
         <v>21031</v>
       </c>
-      <c r="E82" s="1">
+      <c r="E82">
         <v>11148</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -1944,13 +1917,13 @@
         <v>43</v>
       </c>
       <c r="D83">
-        <v>68651</v>
+        <v>72922</v>
       </c>
       <c r="E83">
-        <v>24327</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>25314</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -1961,13 +1934,13 @@
         <v>43</v>
       </c>
       <c r="D84">
-        <v>4673</v>
+        <v>5058</v>
       </c>
       <c r="E84">
-        <v>2431</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -1978,13 +1951,13 @@
         <v>43</v>
       </c>
       <c r="D85">
-        <v>5096</v>
+        <v>5390</v>
       </c>
       <c r="E85">
-        <v>2832</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>5</v>
       </c>
@@ -1995,13 +1968,13 @@
         <v>43</v>
       </c>
       <c r="D86">
-        <v>3237</v>
+        <v>3429</v>
       </c>
       <c r="E86">
-        <v>1579</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -2012,13 +1985,13 @@
         <v>43</v>
       </c>
       <c r="D87">
-        <v>9149</v>
+        <v>10379</v>
       </c>
       <c r="E87">
-        <v>4951</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>5382</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>5</v>
       </c>
@@ -2029,13 +2002,13 @@
         <v>44</v>
       </c>
       <c r="D88">
-        <v>157573</v>
+        <v>168763</v>
       </c>
       <c r="E88">
-        <v>69332</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>72554</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>5</v>
       </c>
@@ -2046,13 +2019,13 @@
         <v>44</v>
       </c>
       <c r="D89">
-        <v>762932</v>
+        <v>816068</v>
       </c>
       <c r="E89">
-        <v>307658</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>321562</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -2063,13 +2036,13 @@
         <v>44</v>
       </c>
       <c r="D90">
-        <v>51248</v>
+        <v>53391</v>
       </c>
       <c r="E90">
-        <v>15632</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>16164</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
         <v>5</v>
       </c>
@@ -2080,13 +2053,13 @@
         <v>44</v>
       </c>
       <c r="D91">
-        <v>5684</v>
+        <v>5819</v>
       </c>
       <c r="E91">
-        <v>2825</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>5</v>
       </c>
@@ -2103,7 +2076,7 @@
         <v>5976</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -2114,13 +2087,13 @@
         <v>44</v>
       </c>
       <c r="D93">
-        <v>9905</v>
+        <v>9936</v>
       </c>
       <c r="E93">
-        <v>4939</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -2131,13 +2104,13 @@
         <v>44</v>
       </c>
       <c r="D94">
-        <v>32298</v>
+        <v>35124</v>
       </c>
       <c r="E94">
-        <v>13198</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>14117</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>5</v>
       </c>
@@ -2148,13 +2121,13 @@
         <v>44</v>
       </c>
       <c r="D95">
-        <v>45469</v>
+        <v>45722</v>
       </c>
       <c r="E95">
-        <v>21306</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>21358</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
         <v>5</v>
       </c>
@@ -2165,13 +2138,13 @@
         <v>44</v>
       </c>
       <c r="D96">
-        <v>157645</v>
+        <v>167876</v>
       </c>
       <c r="E96">
-        <v>61201</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>63586</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>5</v>
       </c>
@@ -2182,13 +2155,13 @@
         <v>44</v>
       </c>
       <c r="D97">
-        <v>3042</v>
+        <v>3290</v>
       </c>
       <c r="E97">
-        <v>1544</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -2199,13 +2172,13 @@
         <v>44</v>
       </c>
       <c r="D98">
-        <v>12644</v>
+        <v>13251</v>
       </c>
       <c r="E98">
-        <v>6176</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6411</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>5</v>
       </c>
@@ -2216,13 +2189,13 @@
         <v>44</v>
       </c>
       <c r="D99">
-        <v>111391</v>
+        <v>119588</v>
       </c>
       <c r="E99">
-        <v>44730</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>46874</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
         <v>5</v>
       </c>
@@ -2233,13 +2206,13 @@
         <v>44</v>
       </c>
       <c r="D100">
-        <v>187021</v>
+        <v>203692</v>
       </c>
       <c r="E100">
-        <v>76163</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>79946</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101" t="s">
         <v>5</v>
       </c>
@@ -2250,13 +2223,13 @@
         <v>44</v>
       </c>
       <c r="D101">
-        <v>145869</v>
+        <v>155358</v>
       </c>
       <c r="E101">
-        <v>63146</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>65915</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -2267,13 +2240,13 @@
         <v>44</v>
       </c>
       <c r="D102">
-        <v>223552</v>
+        <v>236671</v>
       </c>
       <c r="E102">
-        <v>83827</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>87473</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
       <c r="A103" t="s">
         <v>5</v>
       </c>
@@ -2284,13 +2257,13 @@
         <v>44</v>
       </c>
       <c r="D103">
-        <v>189235</v>
+        <v>199605</v>
       </c>
       <c r="E103">
-        <v>86817</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>89663</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
       <c r="A104" t="s">
         <v>5</v>
       </c>
@@ -2301,13 +2274,13 @@
         <v>44</v>
       </c>
       <c r="D104">
-        <v>39263</v>
+        <v>42626</v>
       </c>
       <c r="E104">
-        <v>19153</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>20084</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
       <c r="A105" t="s">
         <v>5</v>
       </c>
@@ -2318,13 +2291,13 @@
         <v>44</v>
       </c>
       <c r="D105">
-        <v>20973</v>
+        <v>23042</v>
       </c>
       <c r="E105">
-        <v>9050</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>9584</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
       <c r="A106" t="s">
         <v>5</v>
       </c>
@@ -2335,13 +2308,13 @@
         <v>44</v>
       </c>
       <c r="D106">
-        <v>17624</v>
+        <v>18325</v>
       </c>
       <c r="E106">
-        <v>9050</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>9281</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
       <c r="A107" t="s">
         <v>5</v>
       </c>
@@ -2352,13 +2325,13 @@
         <v>44</v>
       </c>
       <c r="D107">
-        <v>275904</v>
+        <v>289933</v>
       </c>
       <c r="E107">
-        <v>111473</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>115221</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
       <c r="A108" t="s">
         <v>5</v>
       </c>
@@ -2369,13 +2342,13 @@
         <v>44</v>
       </c>
       <c r="D108">
-        <v>11134</v>
+        <v>11463</v>
       </c>
       <c r="E108">
-        <v>5217</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>5320</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
       <c r="A109" t="s">
         <v>5</v>
       </c>
@@ -2386,13 +2359,13 @@
         <v>44</v>
       </c>
       <c r="D109">
-        <v>113388</v>
+        <v>121857</v>
       </c>
       <c r="E109">
-        <v>45492</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>47621</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
       <c r="A110" t="s">
         <v>5</v>
       </c>
@@ -2403,13 +2376,13 @@
         <v>44</v>
       </c>
       <c r="D110">
-        <v>143583</v>
+        <v>156508</v>
       </c>
       <c r="E110">
-        <v>62176</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>65806</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -2420,13 +2393,13 @@
         <v>44</v>
       </c>
       <c r="D111">
-        <v>286920</v>
+        <v>303308</v>
       </c>
       <c r="E111">
-        <v>107331</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+        <v>111983</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
       <c r="A112" t="s">
         <v>5</v>
       </c>
@@ -2436,14 +2409,14 @@
       <c r="C112" t="s">
         <v>44</v>
       </c>
-      <c r="D112" s="1">
-        <v>176164</v>
-      </c>
-      <c r="E112" s="1">
-        <v>71074</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D112">
+        <v>176202</v>
+      </c>
+      <c r="E112">
+        <v>71084</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -2454,13 +2427,13 @@
         <v>44</v>
       </c>
       <c r="D113">
-        <v>35311</v>
+        <v>38345</v>
       </c>
       <c r="E113">
-        <v>10555</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>11121</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
       <c r="A114" t="s">
         <v>5</v>
       </c>
@@ -2471,13 +2444,13 @@
         <v>44</v>
       </c>
       <c r="D114">
-        <v>175245</v>
+        <v>186636</v>
       </c>
       <c r="E114">
-        <v>67308</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>70056</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
       <c r="A115" t="s">
         <v>5</v>
       </c>
@@ -2488,13 +2461,13 @@
         <v>44</v>
       </c>
       <c r="D115">
-        <v>11590</v>
+        <v>12616</v>
       </c>
       <c r="E115">
-        <v>6234</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6585</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
       <c r="A116" t="s">
         <v>5</v>
       </c>
@@ -2505,13 +2478,13 @@
         <v>44</v>
       </c>
       <c r="D116">
-        <v>2463</v>
+        <v>2509</v>
       </c>
       <c r="E116">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
       <c r="A117" t="s">
         <v>5</v>
       </c>
@@ -2522,13 +2495,13 @@
         <v>44</v>
       </c>
       <c r="D117">
-        <v>4492</v>
+        <v>4827</v>
       </c>
       <c r="E117">
-        <v>1967</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -2539,13 +2512,13 @@
         <v>44</v>
       </c>
       <c r="D118">
-        <v>270095</v>
+        <v>292773</v>
       </c>
       <c r="E118">
-        <v>78053</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>82126</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
       <c r="A119" t="s">
         <v>5</v>
       </c>
@@ -2562,7 +2535,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -2573,13 +2546,13 @@
         <v>45</v>
       </c>
       <c r="D120">
-        <v>24243</v>
+        <v>26128</v>
       </c>
       <c r="E120">
-        <v>14637</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>15747</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -2590,13 +2563,13 @@
         <v>45</v>
       </c>
       <c r="D121">
-        <v>1315</v>
+        <v>1434</v>
       </c>
       <c r="E121">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -2607,13 +2580,13 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>1200</v>
+        <v>1331</v>
       </c>
       <c r="E122">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
       <c r="A123" t="s">
         <v>5</v>
       </c>
@@ -2624,13 +2597,13 @@
         <v>45</v>
       </c>
       <c r="D123">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E123">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -2641,13 +2614,13 @@
         <v>45</v>
       </c>
       <c r="D124">
-        <v>2589</v>
+        <v>2746</v>
       </c>
       <c r="E124">
-        <v>1687</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -2664,7 +2637,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -2681,7 +2654,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5">
       <c r="A127" t="s">
         <v>5</v>
       </c>
@@ -2692,13 +2665,13 @@
         <v>45</v>
       </c>
       <c r="D127">
-        <v>4279</v>
+        <v>4537</v>
       </c>
       <c r="E127">
-        <v>2918</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3095</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
       <c r="A128" t="s">
         <v>5</v>
       </c>
@@ -2709,13 +2682,13 @@
         <v>45</v>
       </c>
       <c r="D128">
-        <v>7997</v>
+        <v>9037</v>
       </c>
       <c r="E128">
-        <v>5155</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>5827</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -2726,13 +2699,13 @@
         <v>45</v>
       </c>
       <c r="D129">
-        <v>614</v>
+        <v>693</v>
       </c>
       <c r="E129">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
       <c r="A130" t="s">
         <v>5</v>
       </c>
@@ -2743,13 +2716,13 @@
         <v>45</v>
       </c>
       <c r="D130">
-        <v>3725</v>
+        <v>4088</v>
       </c>
       <c r="E130">
-        <v>2733</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
       <c r="A131" t="s">
         <v>5</v>
       </c>
@@ -2766,7 +2739,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5">
       <c r="A132" t="s">
         <v>5</v>
       </c>
@@ -2777,13 +2750,13 @@
         <v>45</v>
       </c>
       <c r="D132">
-        <v>2612</v>
+        <v>2725</v>
       </c>
       <c r="E132">
-        <v>1510</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -2800,7 +2773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5">
       <c r="A134" t="s">
         <v>5</v>
       </c>
@@ -2811,13 +2784,13 @@
         <v>45</v>
       </c>
       <c r="D134">
-        <v>478</v>
+        <v>515</v>
       </c>
       <c r="E134">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
       <c r="A135" t="s">
         <v>5</v>
       </c>
@@ -2828,13 +2801,13 @@
         <v>45</v>
       </c>
       <c r="D135">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="E135">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -2845,13 +2818,13 @@
         <v>45</v>
       </c>
       <c r="D136">
-        <v>7971</v>
+        <v>8567</v>
       </c>
       <c r="E136">
-        <v>5127</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>5554</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -2862,13 +2835,13 @@
         <v>45</v>
       </c>
       <c r="D137">
-        <v>802</v>
+        <v>869</v>
       </c>
       <c r="E137">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -2879,13 +2852,13 @@
         <v>45</v>
       </c>
       <c r="D138">
-        <v>5372</v>
+        <v>5812</v>
       </c>
       <c r="E138">
-        <v>3902</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4207</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -2896,13 +2869,13 @@
         <v>45</v>
       </c>
       <c r="D139">
-        <v>4603</v>
+        <v>4871</v>
       </c>
       <c r="E139">
-        <v>3185</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+        <v>3370</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
       <c r="A140" t="s">
         <v>5</v>
       </c>
@@ -2912,14 +2885,14 @@
       <c r="C140" t="s">
         <v>45</v>
       </c>
-      <c r="D140" s="1">
+      <c r="D140">
         <v>3152</v>
       </c>
-      <c r="E140" s="1">
+      <c r="E140">
         <v>2139</v>
       </c>
     </row>
-    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5">
       <c r="A141" t="s">
         <v>5</v>
       </c>
@@ -2930,13 +2903,13 @@
         <v>45</v>
       </c>
       <c r="D141">
-        <v>6081</v>
+        <v>6375</v>
       </c>
       <c r="E141">
-        <v>4962</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>5187</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
       <c r="A142" t="s">
         <v>5</v>
       </c>
@@ -2947,13 +2920,13 @@
         <v>45</v>
       </c>
       <c r="D142">
-        <v>862</v>
+        <v>930</v>
       </c>
       <c r="E142">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
       <c r="A143" t="s">
         <v>5</v>
       </c>
@@ -2964,13 +2937,13 @@
         <v>45</v>
       </c>
       <c r="D143">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="E143">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
       <c r="A144" t="s">
         <v>5</v>
       </c>
@@ -2981,13 +2954,13 @@
         <v>45</v>
       </c>
       <c r="D144">
-        <v>1941</v>
+        <v>2071</v>
       </c>
       <c r="E144">
-        <v>1427</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
       <c r="A145" t="s">
         <v>5</v>
       </c>
@@ -2998,13 +2971,13 @@
         <v>45</v>
       </c>
       <c r="D145">
-        <v>1204</v>
+        <v>1340</v>
       </c>
       <c r="E145">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
       <c r="A146" t="s">
         <v>5</v>
       </c>
@@ -3015,13 +2988,13 @@
         <v>45</v>
       </c>
       <c r="D146">
-        <v>2244</v>
+        <v>2540</v>
       </c>
       <c r="E146">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
       <c r="A147" t="s">
         <v>6</v>
       </c>
@@ -3032,13 +3005,13 @@
         <v>41</v>
       </c>
       <c r="D147">
-        <v>228323</v>
+        <v>245534</v>
       </c>
       <c r="E147">
-        <v>89206</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>93589</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
       <c r="A148" t="s">
         <v>6</v>
       </c>
@@ -3049,13 +3022,13 @@
         <v>41</v>
       </c>
       <c r="D148">
-        <v>931431</v>
+        <v>994292</v>
       </c>
       <c r="E148">
-        <v>351472</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>365521</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
       <c r="A149" t="s">
         <v>6</v>
       </c>
@@ -3066,13 +3039,13 @@
         <v>41</v>
       </c>
       <c r="D149">
-        <v>57377</v>
+        <v>61476</v>
       </c>
       <c r="E149">
-        <v>20065</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>21310</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
       <c r="A150" t="s">
         <v>6</v>
       </c>
@@ -3083,13 +3056,13 @@
         <v>41</v>
       </c>
       <c r="D150">
-        <v>7034</v>
+        <v>7461</v>
       </c>
       <c r="E150">
-        <v>3044</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3140</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
       <c r="A151" t="s">
         <v>6</v>
       </c>
@@ -3100,13 +3073,13 @@
         <v>41</v>
       </c>
       <c r="D151">
-        <v>13928</v>
+        <v>15986</v>
       </c>
       <c r="E151">
-        <v>5955</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6509</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
       <c r="A152" t="s">
         <v>6</v>
       </c>
@@ -3117,13 +3090,13 @@
         <v>41</v>
       </c>
       <c r="D152">
-        <v>14877</v>
+        <v>15134</v>
       </c>
       <c r="E152">
-        <v>6504</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6562</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
       <c r="A153" t="s">
         <v>6</v>
       </c>
@@ -3134,13 +3107,13 @@
         <v>41</v>
       </c>
       <c r="D153">
-        <v>63831</v>
+        <v>68146</v>
       </c>
       <c r="E153">
-        <v>22530</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23572</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
       <c r="A154" t="s">
         <v>6</v>
       </c>
@@ -3151,13 +3124,13 @@
         <v>41</v>
       </c>
       <c r="D154">
-        <v>47421</v>
+        <v>56296</v>
       </c>
       <c r="E154">
-        <v>21905</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>24320</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
       <c r="A155" t="s">
         <v>6</v>
       </c>
@@ -3168,13 +3141,13 @@
         <v>41</v>
       </c>
       <c r="D155">
-        <v>226372</v>
+        <v>241374</v>
       </c>
       <c r="E155">
-        <v>80485</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>83727</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
       <c r="A156" t="s">
         <v>6</v>
       </c>
@@ -3185,13 +3158,13 @@
         <v>41</v>
       </c>
       <c r="D156">
-        <v>4083</v>
+        <v>4535</v>
       </c>
       <c r="E156">
-        <v>1854</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
       <c r="A157" t="s">
         <v>6</v>
       </c>
@@ -3202,13 +3175,13 @@
         <v>41</v>
       </c>
       <c r="D157">
-        <v>11610</v>
+        <v>13563</v>
       </c>
       <c r="E157">
-        <v>5961</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6720</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
       <c r="A158" t="s">
         <v>6</v>
       </c>
@@ -3219,13 +3192,13 @@
         <v>41</v>
       </c>
       <c r="D158">
-        <v>137863</v>
+        <v>146278</v>
       </c>
       <c r="E158">
-        <v>52622</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>54470</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
       <c r="A159" t="s">
         <v>6</v>
       </c>
@@ -3236,13 +3209,13 @@
         <v>41</v>
       </c>
       <c r="D159">
-        <v>301083</v>
+        <v>307075</v>
       </c>
       <c r="E159">
-        <v>83740</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>84911</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
       <c r="A160" t="s">
         <v>6</v>
       </c>
@@ -3253,13 +3226,13 @@
         <v>41</v>
       </c>
       <c r="D160">
-        <v>220125</v>
+        <v>239523</v>
       </c>
       <c r="E160">
-        <v>84332</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>89237</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
       <c r="A161" t="s">
         <v>6</v>
       </c>
@@ -3270,13 +3243,13 @@
         <v>41</v>
       </c>
       <c r="D161">
-        <v>323812</v>
+        <v>346667</v>
       </c>
       <c r="E161">
-        <v>113819</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>118404</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
       <c r="A162" t="s">
         <v>6</v>
       </c>
@@ -3287,13 +3260,13 @@
         <v>41</v>
       </c>
       <c r="D162">
-        <v>5188</v>
+        <v>5814</v>
       </c>
       <c r="E162">
-        <v>2499</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
       <c r="A163" t="s">
         <v>6</v>
       </c>
@@ -3304,13 +3277,13 @@
         <v>41</v>
       </c>
       <c r="D163">
-        <v>242212</v>
+        <v>257212</v>
       </c>
       <c r="E163">
-        <v>103216</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>106677</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
       <c r="A164" t="s">
         <v>6</v>
       </c>
@@ -3321,13 +3294,13 @@
         <v>41</v>
       </c>
       <c r="D164">
-        <v>42900</v>
+        <v>50850</v>
       </c>
       <c r="E164">
-        <v>20682</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23231</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
       <c r="A165" t="s">
         <v>6</v>
       </c>
@@ -3338,13 +3311,13 @@
         <v>41</v>
       </c>
       <c r="D165">
-        <v>24395</v>
+        <v>26241</v>
       </c>
       <c r="E165">
-        <v>9144</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>9548</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
       <c r="A166" t="s">
         <v>6</v>
       </c>
@@ -3355,13 +3328,13 @@
         <v>41</v>
       </c>
       <c r="D166">
-        <v>20497</v>
+        <v>22736</v>
       </c>
       <c r="E166">
-        <v>9670</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>10298</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
       <c r="A167" t="s">
         <v>6</v>
       </c>
@@ -3372,13 +3345,13 @@
         <v>41</v>
       </c>
       <c r="D167">
-        <v>423550</v>
+        <v>463750</v>
       </c>
       <c r="E167">
-        <v>153107</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>161564</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
       <c r="A168" t="s">
         <v>6</v>
       </c>
@@ -3389,13 +3362,13 @@
         <v>41</v>
       </c>
       <c r="D168">
-        <v>13773</v>
+        <v>13790</v>
       </c>
       <c r="E168">
-        <v>5353</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>5354</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
       <c r="A169" t="s">
         <v>6</v>
       </c>
@@ -3406,13 +3379,13 @@
         <v>41</v>
       </c>
       <c r="D169">
-        <v>160272</v>
+        <v>170565</v>
       </c>
       <c r="E169">
-        <v>57738</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>59848</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
       <c r="A170" t="s">
         <v>6</v>
       </c>
@@ -3423,13 +3396,13 @@
         <v>41</v>
       </c>
       <c r="D170">
-        <v>190791</v>
+        <v>205259</v>
       </c>
       <c r="E170">
-        <v>76111</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>79738</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
       <c r="A171" t="s">
         <v>6</v>
       </c>
@@ -3440,13 +3413,13 @@
         <v>41</v>
       </c>
       <c r="D171">
-        <v>363090</v>
+        <v>385517</v>
       </c>
       <c r="E171">
-        <v>142549</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+        <v>148353</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
       <c r="A172" t="s">
         <v>6</v>
       </c>
@@ -3456,14 +3429,14 @@
       <c r="C172" t="s">
         <v>41</v>
       </c>
-      <c r="D172" s="1">
-        <v>230531</v>
-      </c>
-      <c r="E172" s="1">
-        <v>76054</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D172">
+        <v>230715</v>
+      </c>
+      <c r="E172">
+        <v>76080</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
       <c r="A173" t="s">
         <v>6</v>
       </c>
@@ -3474,13 +3447,13 @@
         <v>41</v>
       </c>
       <c r="D173">
-        <v>127902</v>
+        <v>139041</v>
       </c>
       <c r="E173">
-        <v>37477</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>39749</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
       <c r="A174" t="s">
         <v>6</v>
       </c>
@@ -3491,13 +3464,13 @@
         <v>41</v>
       </c>
       <c r="D174">
-        <v>216546</v>
+        <v>229148</v>
       </c>
       <c r="E174">
-        <v>83526</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>86271</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
       <c r="A175" t="s">
         <v>6</v>
       </c>
@@ -3508,13 +3481,13 @@
         <v>41</v>
       </c>
       <c r="D175">
-        <v>16231</v>
+        <v>17738</v>
       </c>
       <c r="E175">
-        <v>8079</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>8630</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
       <c r="A176" t="s">
         <v>6</v>
       </c>
@@ -3525,13 +3498,13 @@
         <v>41</v>
       </c>
       <c r="D176">
-        <v>14929</v>
+        <v>22775</v>
       </c>
       <c r="E176">
-        <v>6282</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>9217</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
       <c r="A177" t="s">
         <v>6</v>
       </c>
@@ -3542,13 +3515,13 @@
         <v>41</v>
       </c>
       <c r="D177">
-        <v>62138</v>
+        <v>67593</v>
       </c>
       <c r="E177">
-        <v>28505</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>30224</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
       <c r="A178" t="s">
         <v>6</v>
       </c>
@@ -3559,13 +3532,13 @@
         <v>41</v>
       </c>
       <c r="D178">
-        <v>309359</v>
+        <v>361666</v>
       </c>
       <c r="E178">
-        <v>88168</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>98116</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
       <c r="A179" t="s">
         <v>6</v>
       </c>
@@ -3576,13 +3549,13 @@
         <v>42</v>
       </c>
       <c r="D179">
-        <v>1724</v>
+        <v>1738</v>
       </c>
       <c r="E179">
-        <v>1510</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
       <c r="A180" t="s">
         <v>6</v>
       </c>
@@ -3593,13 +3566,13 @@
         <v>42</v>
       </c>
       <c r="D180">
-        <v>33153</v>
+        <v>35386</v>
       </c>
       <c r="E180">
-        <v>24031</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>25607</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
       <c r="A181" t="s">
         <v>6</v>
       </c>
@@ -3610,13 +3583,13 @@
         <v>42</v>
       </c>
       <c r="D181">
-        <v>1341</v>
+        <v>1486</v>
       </c>
       <c r="E181">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
       <c r="A182" t="s">
         <v>6</v>
       </c>
@@ -3627,13 +3600,13 @@
         <v>42</v>
       </c>
       <c r="D182">
-        <v>1226</v>
+        <v>1336</v>
       </c>
       <c r="E182">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
       <c r="A183" t="s">
         <v>6</v>
       </c>
@@ -3644,13 +3617,13 @@
         <v>42</v>
       </c>
       <c r="D183">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="E183">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
       <c r="A184" t="s">
         <v>6</v>
       </c>
@@ -3661,13 +3634,13 @@
         <v>42</v>
       </c>
       <c r="D184">
-        <v>3209</v>
+        <v>3447</v>
       </c>
       <c r="E184">
-        <v>2812</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
       <c r="A185" t="s">
         <v>6</v>
       </c>
@@ -3684,7 +3657,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5">
       <c r="A186" t="s">
         <v>6</v>
       </c>
@@ -3701,7 +3674,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5">
       <c r="A187" t="s">
         <v>6</v>
       </c>
@@ -3712,13 +3685,13 @@
         <v>42</v>
       </c>
       <c r="D187">
-        <v>5470</v>
+        <v>5905</v>
       </c>
       <c r="E187">
-        <v>4484</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4835</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
       <c r="A188" t="s">
         <v>6</v>
       </c>
@@ -3729,13 +3702,13 @@
         <v>42</v>
       </c>
       <c r="D188">
-        <v>11696</v>
+        <v>12166</v>
       </c>
       <c r="E188">
-        <v>8181</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>8499</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
       <c r="A189" t="s">
         <v>6</v>
       </c>
@@ -3746,13 +3719,13 @@
         <v>42</v>
       </c>
       <c r="D189">
-        <v>2637</v>
+        <v>2810</v>
       </c>
       <c r="E189">
-        <v>2076</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
       <c r="A190" t="s">
         <v>6</v>
       </c>
@@ -3763,13 +3736,13 @@
         <v>42</v>
       </c>
       <c r="D190">
-        <v>6776</v>
+        <v>7359</v>
       </c>
       <c r="E190">
-        <v>5566</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6049</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
       <c r="A191" t="s">
         <v>6</v>
       </c>
@@ -3786,7 +3759,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5">
       <c r="A192" t="s">
         <v>6</v>
       </c>
@@ -3797,13 +3770,13 @@
         <v>42</v>
       </c>
       <c r="D192">
-        <v>2471</v>
+        <v>2633</v>
       </c>
       <c r="E192">
-        <v>2181</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
       <c r="A193" t="s">
         <v>6</v>
       </c>
@@ -3814,13 +3787,13 @@
         <v>42</v>
       </c>
       <c r="D193">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E193">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
       <c r="A194" t="s">
         <v>6</v>
       </c>
@@ -3831,13 +3804,13 @@
         <v>42</v>
       </c>
       <c r="D194">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E194">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
       <c r="A195" t="s">
         <v>6</v>
       </c>
@@ -3854,7 +3827,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5">
       <c r="A196" t="s">
         <v>6</v>
       </c>
@@ -3865,13 +3838,13 @@
         <v>42</v>
       </c>
       <c r="D196">
-        <v>18000</v>
+        <v>19594</v>
       </c>
       <c r="E196">
-        <v>9270</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>10065</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
       <c r="A197" t="s">
         <v>6</v>
       </c>
@@ -3888,7 +3861,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5">
       <c r="A198" t="s">
         <v>6</v>
       </c>
@@ -3899,13 +3872,13 @@
         <v>42</v>
       </c>
       <c r="D198">
-        <v>1938</v>
+        <v>2077</v>
       </c>
       <c r="E198">
-        <v>1738</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
       <c r="A199" t="s">
         <v>6</v>
       </c>
@@ -3916,13 +3889,13 @@
         <v>42</v>
       </c>
       <c r="D199">
-        <v>10336</v>
+        <v>11244</v>
       </c>
       <c r="E199">
-        <v>7302</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7927</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
       <c r="A200" t="s">
         <v>6</v>
       </c>
@@ -3933,13 +3906,13 @@
         <v>42</v>
       </c>
       <c r="D200">
-        <v>7583</v>
+        <v>7997</v>
       </c>
       <c r="E200">
-        <v>6235</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+        <v>6551</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
       <c r="A201" t="s">
         <v>6</v>
       </c>
@@ -3949,14 +3922,14 @@
       <c r="C201" t="s">
         <v>42</v>
       </c>
-      <c r="D201" s="1">
+      <c r="D201">
         <v>5275</v>
       </c>
-      <c r="E201" s="1">
+      <c r="E201">
         <v>4470</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5">
       <c r="A202" t="s">
         <v>6</v>
       </c>
@@ -3967,13 +3940,13 @@
         <v>42</v>
       </c>
       <c r="D202">
-        <v>23632</v>
+        <v>27701</v>
       </c>
       <c r="E202">
-        <v>7539</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>8418</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
       <c r="A203" t="s">
         <v>6</v>
       </c>
@@ -3984,13 +3957,13 @@
         <v>42</v>
       </c>
       <c r="D203">
-        <v>2351</v>
+        <v>2479</v>
       </c>
       <c r="E203">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
       <c r="A204" t="s">
         <v>6</v>
       </c>
@@ -4001,13 +3974,13 @@
         <v>42</v>
       </c>
       <c r="D204">
-        <v>563</v>
+        <v>618</v>
       </c>
       <c r="E204">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -4018,13 +3991,13 @@
         <v>42</v>
       </c>
       <c r="D205">
-        <v>4229</v>
+        <v>4567</v>
       </c>
       <c r="E205">
-        <v>3001</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
       <c r="A206" t="s">
         <v>6</v>
       </c>
@@ -4035,13 +4008,13 @@
         <v>42</v>
       </c>
       <c r="D206">
-        <v>2505</v>
+        <v>2724</v>
       </c>
       <c r="E206">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
       <c r="A207" t="s">
         <v>6</v>
       </c>
@@ -4052,13 +4025,13 @@
         <v>42</v>
       </c>
       <c r="D207">
-        <v>4909</v>
+        <v>5315</v>
       </c>
       <c r="E207">
-        <v>3674</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3947</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
       <c r="A208" t="s">
         <v>6</v>
       </c>
@@ -4069,13 +4042,13 @@
         <v>43</v>
       </c>
       <c r="D208">
-        <v>15704</v>
+        <v>16487</v>
       </c>
       <c r="E208">
-        <v>6796</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7048</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
       <c r="A209" t="s">
         <v>6</v>
       </c>
@@ -4086,13 +4059,13 @@
         <v>43</v>
       </c>
       <c r="D209">
-        <v>97197</v>
+        <v>104545</v>
       </c>
       <c r="E209">
-        <v>44473</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>46939</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
       <c r="A210" t="s">
         <v>6</v>
       </c>
@@ -4103,13 +4076,13 @@
         <v>43</v>
       </c>
       <c r="D210">
-        <v>1734</v>
+        <v>1954</v>
       </c>
       <c r="E210">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
       <c r="A211" t="s">
         <v>6</v>
       </c>
@@ -4126,7 +4099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5">
       <c r="A212" t="s">
         <v>6</v>
       </c>
@@ -4137,13 +4110,13 @@
         <v>43</v>
       </c>
       <c r="D212">
-        <v>2773</v>
+        <v>2970</v>
       </c>
       <c r="E212">
-        <v>1423</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
       <c r="A213" t="s">
         <v>6</v>
       </c>
@@ -4154,13 +4127,13 @@
         <v>43</v>
       </c>
       <c r="D213">
-        <v>1068</v>
+        <v>1169</v>
       </c>
       <c r="E213">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
       <c r="A214" t="s">
         <v>6</v>
       </c>
@@ -4171,13 +4144,13 @@
         <v>43</v>
       </c>
       <c r="D214">
-        <v>13449</v>
+        <v>15092</v>
       </c>
       <c r="E214">
-        <v>5543</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6311</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
       <c r="A215" t="s">
         <v>6</v>
       </c>
@@ -4194,7 +4167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5">
       <c r="A216" t="s">
         <v>6</v>
       </c>
@@ -4205,13 +4178,13 @@
         <v>43</v>
       </c>
       <c r="D216">
-        <v>13377</v>
+        <v>13922</v>
       </c>
       <c r="E216">
-        <v>6402</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6554</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
       <c r="A217" t="s">
         <v>6</v>
       </c>
@@ -4222,13 +4195,13 @@
         <v>43</v>
       </c>
       <c r="D217">
-        <v>23642</v>
+        <v>26046</v>
       </c>
       <c r="E217">
-        <v>8230</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>8740</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
       <c r="A218" t="s">
         <v>6</v>
       </c>
@@ -4239,13 +4212,13 @@
         <v>43</v>
       </c>
       <c r="D218">
-        <v>8302</v>
+        <v>9043</v>
       </c>
       <c r="E218">
-        <v>3506</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3786</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
       <c r="A219" t="s">
         <v>6</v>
       </c>
@@ -4256,13 +4229,13 @@
         <v>43</v>
       </c>
       <c r="D219">
-        <v>13297</v>
+        <v>14863</v>
       </c>
       <c r="E219">
-        <v>6907</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7555</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
       <c r="A220" t="s">
         <v>6</v>
       </c>
@@ -4273,13 +4246,13 @@
         <v>43</v>
       </c>
       <c r="D220">
-        <v>2156</v>
+        <v>2382</v>
       </c>
       <c r="E220">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
       <c r="A221" t="s">
         <v>6</v>
       </c>
@@ -4290,13 +4263,13 @@
         <v>43</v>
       </c>
       <c r="D221">
-        <v>8236</v>
+        <v>8830</v>
       </c>
       <c r="E221">
-        <v>4428</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4649</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
       <c r="A222" t="s">
         <v>6</v>
       </c>
@@ -4307,13 +4280,13 @@
         <v>43</v>
       </c>
       <c r="D222">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E222">
         <v>14</v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5">
       <c r="A223" t="s">
         <v>6</v>
       </c>
@@ -4324,13 +4297,13 @@
         <v>43</v>
       </c>
       <c r="D223">
-        <v>1362</v>
+        <v>1518</v>
       </c>
       <c r="E223">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
       <c r="A224" t="s">
         <v>6</v>
       </c>
@@ -4341,13 +4314,13 @@
         <v>43</v>
       </c>
       <c r="D224">
-        <v>1346</v>
+        <v>1436</v>
       </c>
       <c r="E224">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
       <c r="A225" t="s">
         <v>6</v>
       </c>
@@ -4358,13 +4331,13 @@
         <v>43</v>
       </c>
       <c r="D225">
-        <v>59355</v>
+        <v>67193</v>
       </c>
       <c r="E225">
-        <v>22947</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>24490</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
       <c r="A226" t="s">
         <v>6</v>
       </c>
@@ -4381,7 +4354,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5">
       <c r="A227" t="s">
         <v>6</v>
       </c>
@@ -4392,13 +4365,13 @@
         <v>43</v>
       </c>
       <c r="D227">
-        <v>7307</v>
+        <v>7881</v>
       </c>
       <c r="E227">
-        <v>3380</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3585</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -4409,13 +4382,13 @@
         <v>43</v>
       </c>
       <c r="D228">
-        <v>38479</v>
+        <v>41381</v>
       </c>
       <c r="E228">
-        <v>19889</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>20938</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
       <c r="A229" t="s">
         <v>6</v>
       </c>
@@ -4426,13 +4399,13 @@
         <v>43</v>
       </c>
       <c r="D229">
-        <v>27357</v>
+        <v>29131</v>
       </c>
       <c r="E229">
-        <v>12370</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+        <v>12849</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
       <c r="A230" t="s">
         <v>6</v>
       </c>
@@ -4442,14 +4415,14 @@
       <c r="C230" t="s">
         <v>43</v>
       </c>
-      <c r="D230" s="1">
+      <c r="D230">
         <v>30940</v>
       </c>
-      <c r="E230" s="1">
+      <c r="E230">
         <v>11975</v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5">
       <c r="A231" t="s">
         <v>6</v>
       </c>
@@ -4460,13 +4433,13 @@
         <v>43</v>
       </c>
       <c r="D231">
-        <v>70789</v>
+        <v>75338</v>
       </c>
       <c r="E231">
-        <v>24413</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>25454</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
       <c r="A232" t="s">
         <v>6</v>
       </c>
@@ -4477,13 +4450,13 @@
         <v>43</v>
       </c>
       <c r="D232">
-        <v>8566</v>
+        <v>9277</v>
       </c>
       <c r="E232">
-        <v>4548</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4803</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
       <c r="A233" t="s">
         <v>6</v>
       </c>
@@ -4494,13 +4467,13 @@
         <v>43</v>
       </c>
       <c r="D233">
-        <v>6290</v>
+        <v>6642</v>
       </c>
       <c r="E233">
-        <v>3115</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3238</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
       <c r="A234" t="s">
         <v>6</v>
       </c>
@@ -4511,13 +4484,13 @@
         <v>43</v>
       </c>
       <c r="D234">
-        <v>5096</v>
+        <v>6358</v>
       </c>
       <c r="E234">
-        <v>2720</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3346</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
       <c r="A235" t="s">
         <v>6</v>
       </c>
@@ -4528,13 +4501,13 @@
         <v>43</v>
       </c>
       <c r="D235">
-        <v>7614</v>
+        <v>8618</v>
       </c>
       <c r="E235">
-        <v>3942</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4355</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
       <c r="A236" t="s">
         <v>6</v>
       </c>
@@ -4545,13 +4518,13 @@
         <v>43</v>
       </c>
       <c r="D236">
-        <v>16196</v>
+        <v>18886</v>
       </c>
       <c r="E236">
-        <v>6826</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7409</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
       <c r="A237" t="s">
         <v>6</v>
       </c>
@@ -4562,13 +4535,13 @@
         <v>44</v>
       </c>
       <c r="D237">
-        <v>212619</v>
+        <v>229047</v>
       </c>
       <c r="E237">
-        <v>85644</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>89957</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
       <c r="A238" t="s">
         <v>6</v>
       </c>
@@ -4579,13 +4552,13 @@
         <v>44</v>
       </c>
       <c r="D238">
-        <v>834234</v>
+        <v>889747</v>
       </c>
       <c r="E238">
-        <v>332619</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>346016</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
       <c r="A239" t="s">
         <v>6</v>
       </c>
@@ -4596,13 +4569,13 @@
         <v>44</v>
       </c>
       <c r="D239">
-        <v>55643</v>
+        <v>59522</v>
       </c>
       <c r="E239">
-        <v>19454</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>20651</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
       <c r="A240" t="s">
         <v>6</v>
       </c>
@@ -4613,13 +4586,13 @@
         <v>44</v>
       </c>
       <c r="D240">
-        <v>7034</v>
+        <v>7461</v>
       </c>
       <c r="E240">
-        <v>3044</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3140</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
       <c r="A241" t="s">
         <v>6</v>
       </c>
@@ -4630,13 +4603,13 @@
         <v>44</v>
       </c>
       <c r="D241">
-        <v>13928</v>
+        <v>15986</v>
       </c>
       <c r="E241">
-        <v>5955</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6509</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
       <c r="A242" t="s">
         <v>6</v>
       </c>
@@ -4647,13 +4620,13 @@
         <v>44</v>
       </c>
       <c r="D242">
-        <v>14876</v>
+        <v>15133</v>
       </c>
       <c r="E242">
-        <v>6503</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6561</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
       <c r="A243" t="s">
         <v>6</v>
       </c>
@@ -4664,13 +4637,13 @@
         <v>44</v>
       </c>
       <c r="D243">
-        <v>61058</v>
+        <v>65176</v>
       </c>
       <c r="E243">
-        <v>21963</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>22992</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
       <c r="A244" t="s">
         <v>6</v>
       </c>
@@ -4681,13 +4654,13 @@
         <v>44</v>
       </c>
       <c r="D244">
-        <v>46353</v>
+        <v>55127</v>
       </c>
       <c r="E244">
-        <v>21735</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>24146</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
       <c r="A245" t="s">
         <v>6</v>
       </c>
@@ -4698,13 +4671,13 @@
         <v>44</v>
       </c>
       <c r="D245">
-        <v>212923</v>
+        <v>226282</v>
       </c>
       <c r="E245">
-        <v>78201</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>81092</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
       <c r="A246" t="s">
         <v>6</v>
       </c>
@@ -4715,13 +4688,13 @@
         <v>44</v>
       </c>
       <c r="D246">
-        <v>4083</v>
+        <v>4535</v>
       </c>
       <c r="E246">
-        <v>1854</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
       <c r="A247" t="s">
         <v>6</v>
       </c>
@@ -4732,13 +4705,13 @@
         <v>44</v>
       </c>
       <c r="D247">
-        <v>11609</v>
+        <v>13562</v>
       </c>
       <c r="E247">
-        <v>5960</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6719</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
       <c r="A248" t="s">
         <v>6</v>
       </c>
@@ -4749,13 +4722,13 @@
         <v>44</v>
       </c>
       <c r="D248">
-        <v>124486</v>
+        <v>132356</v>
       </c>
       <c r="E248">
-        <v>49032</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>50834</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
       <c r="A249" t="s">
         <v>6</v>
       </c>
@@ -4766,13 +4739,13 @@
         <v>44</v>
       </c>
       <c r="D249">
-        <v>277441</v>
+        <v>281029</v>
       </c>
       <c r="E249">
-        <v>79411</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>80322</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
       <c r="A250" t="s">
         <v>6</v>
       </c>
@@ -4783,13 +4756,13 @@
         <v>44</v>
       </c>
       <c r="D250">
-        <v>211823</v>
+        <v>230480</v>
       </c>
       <c r="E250">
-        <v>82909</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>87733</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
       <c r="A251" t="s">
         <v>6</v>
       </c>
@@ -4800,13 +4773,13 @@
         <v>44</v>
       </c>
       <c r="D251">
-        <v>310515</v>
+        <v>331804</v>
       </c>
       <c r="E251">
-        <v>111116</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>115442</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
       <c r="A252" t="s">
         <v>6</v>
       </c>
@@ -4817,13 +4790,13 @@
         <v>44</v>
       </c>
       <c r="D252">
-        <v>3032</v>
+        <v>3432</v>
       </c>
       <c r="E252">
-        <v>1525</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
       <c r="A253" t="s">
         <v>6</v>
       </c>
@@ -4834,13 +4807,13 @@
         <v>44</v>
       </c>
       <c r="D253">
-        <v>233976</v>
+        <v>248382</v>
       </c>
       <c r="E253">
-        <v>101484</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>104908</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
       <c r="A254" t="s">
         <v>6</v>
       </c>
@@ -4851,13 +4824,13 @@
         <v>44</v>
       </c>
       <c r="D254">
-        <v>42871</v>
+        <v>50819</v>
       </c>
       <c r="E254">
-        <v>20673</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23223</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
       <c r="A255" t="s">
         <v>6</v>
       </c>
@@ -4868,13 +4841,13 @@
         <v>44</v>
       </c>
       <c r="D255">
-        <v>23033</v>
+        <v>24723</v>
       </c>
       <c r="E255">
-        <v>8931</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>9320</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
       <c r="A256" t="s">
         <v>6</v>
       </c>
@@ -4885,13 +4858,13 @@
         <v>44</v>
       </c>
       <c r="D256">
-        <v>19151</v>
+        <v>21300</v>
       </c>
       <c r="E256">
-        <v>9259</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>9872</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
       <c r="A257" t="s">
         <v>6</v>
       </c>
@@ -4902,13 +4875,13 @@
         <v>44</v>
       </c>
       <c r="D257">
-        <v>364195</v>
+        <v>396557</v>
       </c>
       <c r="E257">
-        <v>143475</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>151439</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
       <c r="A258" t="s">
         <v>6</v>
       </c>
@@ -4919,13 +4892,13 @@
         <v>44</v>
       </c>
       <c r="D258">
-        <v>11358</v>
+        <v>11375</v>
       </c>
       <c r="E258">
-        <v>5021</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>5022</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
       <c r="A259" t="s">
         <v>6</v>
       </c>
@@ -4936,13 +4909,13 @@
         <v>44</v>
       </c>
       <c r="D259">
-        <v>152965</v>
+        <v>162684</v>
       </c>
       <c r="E259">
-        <v>56594</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>58642</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
       <c r="A260" t="s">
         <v>6</v>
       </c>
@@ -4953,13 +4926,13 @@
         <v>44</v>
       </c>
       <c r="D260">
-        <v>152312</v>
+        <v>163878</v>
       </c>
       <c r="E260">
-        <v>64622</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>67832</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
       <c r="A261" t="s">
         <v>6</v>
       </c>
@@ -4970,13 +4943,13 @@
         <v>44</v>
       </c>
       <c r="D261">
-        <v>335733</v>
+        <v>356386</v>
       </c>
       <c r="E261">
-        <v>136876</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+        <v>142590</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
       <c r="A262" t="s">
         <v>6</v>
       </c>
@@ -4986,14 +4959,14 @@
       <c r="C262" t="s">
         <v>44</v>
       </c>
-      <c r="D262" s="1">
-        <v>199591</v>
-      </c>
-      <c r="E262" s="1">
-        <v>69970</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D262">
+        <v>199775</v>
+      </c>
+      <c r="E262">
+        <v>69996</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
       <c r="A263" t="s">
         <v>6</v>
       </c>
@@ -5004,13 +4977,13 @@
         <v>44</v>
       </c>
       <c r="D263">
-        <v>57113</v>
+        <v>63703</v>
       </c>
       <c r="E263">
-        <v>19334</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>21252</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
       <c r="A264" t="s">
         <v>6</v>
       </c>
@@ -5021,13 +4994,13 @@
         <v>44</v>
       </c>
       <c r="D264">
-        <v>207980</v>
+        <v>219871</v>
       </c>
       <c r="E264">
-        <v>81407</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>84033</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
       <c r="A265" t="s">
         <v>6</v>
       </c>
@@ -5038,13 +5011,13 @@
         <v>44</v>
       </c>
       <c r="D265">
-        <v>9941</v>
+        <v>11096</v>
       </c>
       <c r="E265">
-        <v>5599</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6069</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
       <c r="A266" t="s">
         <v>6</v>
       </c>
@@ -5055,13 +5028,13 @@
         <v>44</v>
       </c>
       <c r="D266">
-        <v>9833</v>
+        <v>16417</v>
       </c>
       <c r="E266">
-        <v>4397</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7516</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
       <c r="A267" t="s">
         <v>6</v>
       </c>
@@ -5072,13 +5045,13 @@
         <v>44</v>
       </c>
       <c r="D267">
-        <v>54524</v>
+        <v>58975</v>
       </c>
       <c r="E267">
-        <v>26023</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>27553</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
       <c r="A268" t="s">
         <v>6</v>
       </c>
@@ -5089,13 +5062,13 @@
         <v>44</v>
       </c>
       <c r="D268">
-        <v>293163</v>
+        <v>342780</v>
       </c>
       <c r="E268">
-        <v>84937</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>94733</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
       <c r="A269" t="s">
         <v>6</v>
       </c>
@@ -5112,7 +5085,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5">
       <c r="A270" t="s">
         <v>6</v>
       </c>
@@ -5123,13 +5096,13 @@
         <v>45</v>
       </c>
       <c r="D270">
-        <v>23058</v>
+        <v>24742</v>
       </c>
       <c r="E270">
-        <v>13850</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>14824</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
       <c r="A271" t="s">
         <v>6</v>
       </c>
@@ -5140,13 +5113,13 @@
         <v>45</v>
       </c>
       <c r="D271">
-        <v>1286</v>
+        <v>1421</v>
       </c>
       <c r="E271">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
       <c r="A272" t="s">
         <v>6</v>
       </c>
@@ -5157,13 +5130,13 @@
         <v>45</v>
       </c>
       <c r="D272">
-        <v>674</v>
+        <v>722</v>
       </c>
       <c r="E272">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
       <c r="A273" t="s">
         <v>6</v>
       </c>
@@ -5174,13 +5147,13 @@
         <v>45</v>
       </c>
       <c r="D273">
+        <v>12</v>
+      </c>
+      <c r="E273">
         <v>10</v>
       </c>
-      <c r="E273">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="274" spans="1:5">
       <c r="A274" t="s">
         <v>6</v>
       </c>
@@ -5191,13 +5164,13 @@
         <v>45</v>
       </c>
       <c r="D274">
-        <v>2622</v>
+        <v>2842</v>
       </c>
       <c r="E274">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
       <c r="A275" t="s">
         <v>6</v>
       </c>
@@ -5214,7 +5187,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5">
       <c r="A276" t="s">
         <v>6</v>
       </c>
@@ -5231,7 +5204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5">
       <c r="A277" t="s">
         <v>6</v>
       </c>
@@ -5242,13 +5215,13 @@
         <v>45</v>
       </c>
       <c r="D277">
-        <v>3879</v>
+        <v>4229</v>
       </c>
       <c r="E277">
-        <v>2689</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
       <c r="A278" t="s">
         <v>6</v>
       </c>
@@ -5259,13 +5232,13 @@
         <v>45</v>
       </c>
       <c r="D278">
-        <v>7651</v>
+        <v>7975</v>
       </c>
       <c r="E278">
-        <v>5083</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>5314</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
       <c r="A279" t="s">
         <v>6</v>
       </c>
@@ -5276,13 +5249,13 @@
         <v>45</v>
       </c>
       <c r="D279">
-        <v>1444</v>
+        <v>1560</v>
       </c>
       <c r="E279">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
       <c r="A280" t="s">
         <v>6</v>
       </c>
@@ -5293,13 +5266,13 @@
         <v>45</v>
       </c>
       <c r="D280">
-        <v>2784</v>
+        <v>3106</v>
       </c>
       <c r="E280">
-        <v>2195</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
       <c r="A281" t="s">
         <v>6</v>
       </c>
@@ -5316,7 +5289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5">
       <c r="A282" t="s">
         <v>6</v>
       </c>
@@ -5327,13 +5300,13 @@
         <v>45</v>
       </c>
       <c r="D282">
-        <v>1725</v>
+        <v>1850</v>
       </c>
       <c r="E282">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
       <c r="A283" t="s">
         <v>6</v>
       </c>
@@ -5344,13 +5317,13 @@
         <v>45</v>
       </c>
       <c r="D283">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E283">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
       <c r="A284" t="s">
         <v>6</v>
       </c>
@@ -5361,13 +5334,13 @@
         <v>45</v>
       </c>
       <c r="D284">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E284">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
       <c r="A285" t="s">
         <v>6</v>
       </c>
@@ -5384,7 +5357,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5">
       <c r="A286" t="s">
         <v>6</v>
       </c>
@@ -5395,13 +5368,13 @@
         <v>45</v>
       </c>
       <c r="D286">
-        <v>7946</v>
+        <v>8610</v>
       </c>
       <c r="E286">
-        <v>5659</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6147</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
       <c r="A287" t="s">
         <v>6</v>
       </c>
@@ -5412,13 +5385,13 @@
         <v>45</v>
       </c>
       <c r="D287">
-        <v>1461</v>
+        <v>1590</v>
       </c>
       <c r="E287">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
       <c r="A288" t="s">
         <v>6</v>
       </c>
@@ -5429,13 +5402,13 @@
         <v>45</v>
       </c>
       <c r="D288">
-        <v>5825</v>
+        <v>6591</v>
       </c>
       <c r="E288">
-        <v>4404</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4871</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
       <c r="A289" t="s">
         <v>6</v>
       </c>
@@ -5446,13 +5419,13 @@
         <v>45</v>
       </c>
       <c r="D289">
-        <v>4232</v>
+        <v>4443</v>
       </c>
       <c r="E289">
-        <v>2901</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+        <v>3033</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
       <c r="A290" t="s">
         <v>6</v>
       </c>
@@ -5462,14 +5435,14 @@
       <c r="C290" t="s">
         <v>45</v>
       </c>
-      <c r="D290" s="1">
+      <c r="D290">
         <v>3359</v>
       </c>
-      <c r="E290" s="1">
+      <c r="E290">
         <v>2425</v>
       </c>
     </row>
-    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5">
       <c r="A291" t="s">
         <v>6</v>
       </c>
@@ -5480,13 +5453,13 @@
         <v>45</v>
       </c>
       <c r="D291">
-        <v>5539</v>
+        <v>6275</v>
       </c>
       <c r="E291">
-        <v>4580</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>5167</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
       <c r="A292" t="s">
         <v>6</v>
       </c>
@@ -5497,13 +5470,13 @@
         <v>45</v>
       </c>
       <c r="D292">
-        <v>947</v>
+        <v>1005</v>
       </c>
       <c r="E292">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
       <c r="A293" t="s">
         <v>6</v>
       </c>
@@ -5514,13 +5487,13 @@
         <v>45</v>
       </c>
       <c r="D293">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="E293">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
       <c r="A294" t="s">
         <v>6</v>
       </c>
@@ -5531,13 +5504,13 @@
         <v>45</v>
       </c>
       <c r="D294">
-        <v>2078</v>
+        <v>2231</v>
       </c>
       <c r="E294">
-        <v>1488</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
       <c r="A295" t="s">
         <v>6</v>
       </c>
@@ -5548,13 +5521,13 @@
         <v>45</v>
       </c>
       <c r="D295">
-        <v>1294</v>
+        <v>1421</v>
       </c>
       <c r="E295">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
       <c r="A296" t="s">
         <v>6</v>
       </c>
@@ -5565,13 +5538,13 @@
         <v>45</v>
       </c>
       <c r="D296">
-        <v>2899</v>
+        <v>3121</v>
       </c>
       <c r="E296">
-        <v>2099</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
       <c r="A297" t="s">
         <v>7</v>
       </c>
@@ -5582,13 +5555,13 @@
         <v>41</v>
       </c>
       <c r="D297">
-        <v>295512</v>
+        <v>318116</v>
       </c>
       <c r="E297">
-        <v>106606</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>111101</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
       <c r="A298" t="s">
         <v>7</v>
       </c>
@@ -5599,13 +5572,13 @@
         <v>41</v>
       </c>
       <c r="D298">
-        <v>956097</v>
+        <v>1026374</v>
       </c>
       <c r="E298">
-        <v>339135</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>355247</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
       <c r="A299" t="s">
         <v>7</v>
       </c>
@@ -5616,13 +5589,13 @@
         <v>41</v>
       </c>
       <c r="D299">
-        <v>80792</v>
+        <v>86274</v>
       </c>
       <c r="E299">
-        <v>25680</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>27032</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
       <c r="A300" t="s">
         <v>7</v>
       </c>
@@ -5633,13 +5606,13 @@
         <v>41</v>
       </c>
       <c r="D300">
-        <v>7061</v>
+        <v>7344</v>
       </c>
       <c r="E300">
-        <v>3635</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
       <c r="A301" t="s">
         <v>7</v>
       </c>
@@ -5650,13 +5623,13 @@
         <v>41</v>
       </c>
       <c r="D301">
-        <v>13262</v>
+        <v>14539</v>
       </c>
       <c r="E301">
-        <v>5750</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6008</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
       <c r="A302" t="s">
         <v>7</v>
       </c>
@@ -5667,13 +5640,13 @@
         <v>41</v>
       </c>
       <c r="D302">
-        <v>17262</v>
+        <v>18569</v>
       </c>
       <c r="E302">
-        <v>7502</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7874</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
       <c r="A303" t="s">
         <v>7</v>
       </c>
@@ -5684,13 +5657,13 @@
         <v>41</v>
       </c>
       <c r="D303">
-        <v>78615</v>
+        <v>84362</v>
       </c>
       <c r="E303">
-        <v>26176</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>27345</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
       <c r="A304" t="s">
         <v>7</v>
       </c>
@@ -5701,13 +5674,13 @@
         <v>41</v>
       </c>
       <c r="D304">
-        <v>51998</v>
+        <v>56619</v>
       </c>
       <c r="E304">
-        <v>23298</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>24424</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
       <c r="A305" t="s">
         <v>7</v>
       </c>
@@ -5718,13 +5691,13 @@
         <v>41</v>
       </c>
       <c r="D305">
-        <v>311602</v>
+        <v>333824</v>
       </c>
       <c r="E305">
-        <v>101160</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>104835</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
       <c r="A306" t="s">
         <v>7</v>
       </c>
@@ -5735,13 +5708,13 @@
         <v>41</v>
       </c>
       <c r="D306">
-        <v>4212</v>
+        <v>4898</v>
       </c>
       <c r="E306">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
       <c r="A307" t="s">
         <v>7</v>
       </c>
@@ -5752,13 +5725,13 @@
         <v>41</v>
       </c>
       <c r="D307">
-        <v>15037</v>
+        <v>16550</v>
       </c>
       <c r="E307">
-        <v>7180</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7581</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
       <c r="A308" t="s">
         <v>7</v>
       </c>
@@ -5769,13 +5742,13 @@
         <v>41</v>
       </c>
       <c r="D308">
-        <v>147133</v>
+        <v>157307</v>
       </c>
       <c r="E308">
-        <v>54347</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>56470</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
       <c r="A309" t="s">
         <v>7</v>
       </c>
@@ -5786,13 +5759,13 @@
         <v>41</v>
       </c>
       <c r="D309">
-        <v>351798</v>
+        <v>373787</v>
       </c>
       <c r="E309">
-        <v>91848</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>95267</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
       <c r="A310" t="s">
         <v>7</v>
       </c>
@@ -5803,13 +5776,13 @@
         <v>41</v>
       </c>
       <c r="D310">
-        <v>266569</v>
+        <v>284596</v>
       </c>
       <c r="E310">
-        <v>98949</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>102624</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
       <c r="A311" t="s">
         <v>7</v>
       </c>
@@ -5820,13 +5793,13 @@
         <v>41</v>
       </c>
       <c r="D311">
-        <v>423490</v>
+        <v>449797</v>
       </c>
       <c r="E311">
-        <v>137328</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>141881</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
       <c r="A312" t="s">
         <v>7</v>
       </c>
@@ -5837,13 +5810,13 @@
         <v>41</v>
       </c>
       <c r="D312">
-        <v>20104</v>
+        <v>21512</v>
       </c>
       <c r="E312">
-        <v>6349</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6598</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
       <c r="A313" t="s">
         <v>7</v>
       </c>
@@ -5854,13 +5827,13 @@
         <v>41</v>
       </c>
       <c r="D313">
-        <v>264401</v>
+        <v>282174</v>
       </c>
       <c r="E313">
-        <v>106449</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>110508</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
       <c r="A314" t="s">
         <v>7</v>
       </c>
@@ -5871,13 +5844,13 @@
         <v>41</v>
       </c>
       <c r="D314">
-        <v>46917</v>
+        <v>49041</v>
       </c>
       <c r="E314">
-        <v>21987</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>22536</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
       <c r="A315" t="s">
         <v>7</v>
       </c>
@@ -5888,13 +5861,13 @@
         <v>41</v>
       </c>
       <c r="D315">
-        <v>32979</v>
+        <v>34882</v>
       </c>
       <c r="E315">
-        <v>10232</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>10590</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
       <c r="A316" t="s">
         <v>7</v>
       </c>
@@ -5905,13 +5878,13 @@
         <v>41</v>
       </c>
       <c r="D316">
-        <v>22046</v>
+        <v>23721</v>
       </c>
       <c r="E316">
-        <v>10337</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>10819</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
       <c r="A317" t="s">
         <v>7</v>
       </c>
@@ -5922,13 +5895,13 @@
         <v>41</v>
       </c>
       <c r="D317">
-        <v>698345</v>
+        <v>757427</v>
       </c>
       <c r="E317">
-        <v>209604</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>219181</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
       <c r="A318" t="s">
         <v>7</v>
       </c>
@@ -5939,13 +5912,13 @@
         <v>41</v>
       </c>
       <c r="D318">
-        <v>20883</v>
+        <v>22690</v>
       </c>
       <c r="E318">
-        <v>7199</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7590</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
       <c r="A319" t="s">
         <v>7</v>
       </c>
@@ -5956,13 +5929,13 @@
         <v>41</v>
       </c>
       <c r="D319">
-        <v>206538</v>
+        <v>221788</v>
       </c>
       <c r="E319">
-        <v>68169</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>70833</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
       <c r="A320" t="s">
         <v>7</v>
       </c>
@@ -5973,13 +5946,13 @@
         <v>41</v>
       </c>
       <c r="D320">
-        <v>231394</v>
+        <v>246670</v>
       </c>
       <c r="E320">
-        <v>85682</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>89164</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
       <c r="A321" t="s">
         <v>7</v>
       </c>
@@ -5990,30 +5963,30 @@
         <v>41</v>
       </c>
       <c r="D321">
-        <v>583948</v>
+        <v>620113</v>
       </c>
       <c r="E321">
-        <v>190457</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A322" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B322" s="2" t="s">
+        <v>197510</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" t="s">
+        <v>7</v>
+      </c>
+      <c r="B322" t="s">
         <v>32</v>
       </c>
-      <c r="C322" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D322" s="3">
-        <v>217636</v>
-      </c>
-      <c r="E322" s="3">
-        <v>74993</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C322" t="s">
+        <v>41</v>
+      </c>
+      <c r="D322">
+        <v>235960</v>
+      </c>
+      <c r="E322">
+        <v>78974</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
       <c r="A323" t="s">
         <v>7</v>
       </c>
@@ -6024,13 +5997,13 @@
         <v>41</v>
       </c>
       <c r="D323">
-        <v>207676</v>
+        <v>232185</v>
       </c>
       <c r="E323">
-        <v>59399</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>62683</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
       <c r="A324" t="s">
         <v>7</v>
       </c>
@@ -6041,13 +6014,13 @@
         <v>41</v>
       </c>
       <c r="D324">
-        <v>223850</v>
+        <v>238373</v>
       </c>
       <c r="E324">
-        <v>85529</v>
-      </c>
-    </row>
-    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>88516</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
       <c r="A325" t="s">
         <v>7</v>
       </c>
@@ -6058,13 +6031,13 @@
         <v>41</v>
       </c>
       <c r="D325">
-        <v>21619</v>
+        <v>23139</v>
       </c>
       <c r="E325">
-        <v>10046</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>10492</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
       <c r="A326" t="s">
         <v>7</v>
       </c>
@@ -6075,13 +6048,13 @@
         <v>41</v>
       </c>
       <c r="D326">
-        <v>162540</v>
+        <v>174829</v>
       </c>
       <c r="E326">
-        <v>48824</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>51044</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
       <c r="A327" t="s">
         <v>7</v>
       </c>
@@ -6092,13 +6065,13 @@
         <v>41</v>
       </c>
       <c r="D327">
-        <v>142488</v>
+        <v>152589</v>
       </c>
       <c r="E327">
-        <v>54249</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>56487</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
       <c r="A328" t="s">
         <v>7</v>
       </c>
@@ -6109,13 +6082,13 @@
         <v>41</v>
       </c>
       <c r="D328">
-        <v>336166</v>
+        <v>359441</v>
       </c>
       <c r="E328">
-        <v>100184</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>104035</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
       <c r="A329" t="s">
         <v>7</v>
       </c>
@@ -6126,13 +6099,13 @@
         <v>42</v>
       </c>
       <c r="D329">
-        <v>2536</v>
+        <v>2707</v>
       </c>
       <c r="E329">
-        <v>2175</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
       <c r="A330" t="s">
         <v>7</v>
       </c>
@@ -6143,13 +6116,13 @@
         <v>42</v>
       </c>
       <c r="D330">
-        <v>34233</v>
+        <v>36601</v>
       </c>
       <c r="E330">
-        <v>25685</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>27473</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
       <c r="A331" t="s">
         <v>7</v>
       </c>
@@ -6160,13 +6133,13 @@
         <v>42</v>
       </c>
       <c r="D331">
-        <v>1587</v>
+        <v>1716</v>
       </c>
       <c r="E331">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
       <c r="A332" t="s">
         <v>7</v>
       </c>
@@ -6177,13 +6150,13 @@
         <v>42</v>
       </c>
       <c r="D332">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E332">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
       <c r="A333" t="s">
         <v>7</v>
       </c>
@@ -6194,13 +6167,13 @@
         <v>42</v>
       </c>
       <c r="D333">
-        <v>1655</v>
+        <v>1757</v>
       </c>
       <c r="E333">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
       <c r="A334" t="s">
         <v>7</v>
       </c>
@@ -6211,13 +6184,13 @@
         <v>42</v>
       </c>
       <c r="D334">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="E334">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
       <c r="A335" t="s">
         <v>7</v>
       </c>
@@ -6228,13 +6201,13 @@
         <v>42</v>
       </c>
       <c r="D335">
-        <v>5891</v>
+        <v>6227</v>
       </c>
       <c r="E335">
-        <v>5110</v>
-      </c>
-    </row>
-    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>5398</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
       <c r="A336" t="s">
         <v>7</v>
       </c>
@@ -6245,13 +6218,13 @@
         <v>42</v>
       </c>
       <c r="D336">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E336">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
       <c r="A337" t="s">
         <v>7</v>
       </c>
@@ -6268,7 +6241,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:5">
       <c r="A338" t="s">
         <v>7</v>
       </c>
@@ -6279,13 +6252,13 @@
         <v>42</v>
       </c>
       <c r="D338">
-        <v>5560</v>
+        <v>6047</v>
       </c>
       <c r="E338">
-        <v>4562</v>
-      </c>
-    </row>
-    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4951</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
       <c r="A339" t="s">
         <v>7</v>
       </c>
@@ -6296,13 +6269,13 @@
         <v>42</v>
       </c>
       <c r="D339">
-        <v>10244</v>
+        <v>10620</v>
       </c>
       <c r="E339">
-        <v>7421</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7656</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
       <c r="A340" t="s">
         <v>7</v>
       </c>
@@ -6313,13 +6286,13 @@
         <v>42</v>
       </c>
       <c r="D340">
-        <v>3457</v>
+        <v>3613</v>
       </c>
       <c r="E340">
-        <v>2658</v>
-      </c>
-    </row>
-    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2786</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
       <c r="A341" t="s">
         <v>7</v>
       </c>
@@ -6330,13 +6303,13 @@
         <v>42</v>
       </c>
       <c r="D341">
-        <v>8039</v>
+        <v>8783</v>
       </c>
       <c r="E341">
-        <v>6442</v>
-      </c>
-    </row>
-    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6994</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
       <c r="A342" t="s">
         <v>7</v>
       </c>
@@ -6353,7 +6326,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:5">
       <c r="A343" t="s">
         <v>7</v>
       </c>
@@ -6364,13 +6337,13 @@
         <v>42</v>
       </c>
       <c r="D343">
-        <v>2276</v>
+        <v>2448</v>
       </c>
       <c r="E343">
-        <v>1872</v>
-      </c>
-    </row>
-    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
       <c r="A344" t="s">
         <v>7</v>
       </c>
@@ -6381,13 +6354,13 @@
         <v>42</v>
       </c>
       <c r="D344">
+        <v>106</v>
+      </c>
+      <c r="E344">
         <v>95</v>
       </c>
-      <c r="E344">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="345" spans="1:5">
       <c r="A345" t="s">
         <v>7</v>
       </c>
@@ -6398,13 +6371,13 @@
         <v>42</v>
       </c>
       <c r="D345">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="E345">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
       <c r="A346" t="s">
         <v>7</v>
       </c>
@@ -6421,7 +6394,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:5">
       <c r="A347" t="s">
         <v>7</v>
       </c>
@@ -6432,13 +6405,13 @@
         <v>42</v>
       </c>
       <c r="D347">
-        <v>21360</v>
+        <v>23264</v>
       </c>
       <c r="E347">
-        <v>10455</v>
-      </c>
-    </row>
-    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>11338</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
       <c r="A348" t="s">
         <v>7</v>
       </c>
@@ -6449,13 +6422,13 @@
         <v>42</v>
       </c>
       <c r="D348">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="E348">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
       <c r="A349" t="s">
         <v>7</v>
       </c>
@@ -6466,13 +6439,13 @@
         <v>42</v>
       </c>
       <c r="D349">
-        <v>1822</v>
+        <v>2024</v>
       </c>
       <c r="E349">
-        <v>1648</v>
-      </c>
-    </row>
-    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
       <c r="A350" t="s">
         <v>7</v>
       </c>
@@ -6483,13 +6456,13 @@
         <v>42</v>
       </c>
       <c r="D350">
-        <v>10495</v>
+        <v>11261</v>
       </c>
       <c r="E350">
-        <v>7293</v>
-      </c>
-    </row>
-    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7742</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
       <c r="A351" t="s">
         <v>7</v>
       </c>
@@ -6500,30 +6473,30 @@
         <v>42</v>
       </c>
       <c r="D351">
-        <v>8192</v>
+        <v>8603</v>
       </c>
       <c r="E351">
-        <v>6795</v>
-      </c>
-    </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A352" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B352" s="2" t="s">
+        <v>7106</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" t="s">
+        <v>7</v>
+      </c>
+      <c r="B352" t="s">
         <v>32</v>
       </c>
-      <c r="C352" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D352" s="3">
-        <v>5634</v>
-      </c>
-      <c r="E352" s="3">
-        <v>4690</v>
-      </c>
-    </row>
-    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C352" t="s">
+        <v>42</v>
+      </c>
+      <c r="D352">
+        <v>6222</v>
+      </c>
+      <c r="E352">
+        <v>5181</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
       <c r="A353" t="s">
         <v>7</v>
       </c>
@@ -6534,13 +6507,13 @@
         <v>42</v>
       </c>
       <c r="D353">
-        <v>23186</v>
+        <v>26109</v>
       </c>
       <c r="E353">
-        <v>6614</v>
-      </c>
-    </row>
-    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7410</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
       <c r="A354" t="s">
         <v>7</v>
       </c>
@@ -6551,13 +6524,13 @@
         <v>42</v>
       </c>
       <c r="D354">
-        <v>2335</v>
+        <v>2485</v>
       </c>
       <c r="E354">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
       <c r="A355" t="s">
         <v>7</v>
       </c>
@@ -6568,13 +6541,13 @@
         <v>42</v>
       </c>
       <c r="D355">
-        <v>624</v>
+        <v>675</v>
       </c>
       <c r="E355">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
       <c r="A356" t="s">
         <v>7</v>
       </c>
@@ -6585,13 +6558,13 @@
         <v>42</v>
       </c>
       <c r="D356">
-        <v>4374</v>
+        <v>4670</v>
       </c>
       <c r="E356">
-        <v>3483</v>
-      </c>
-    </row>
-    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3719</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
       <c r="A357" t="s">
         <v>7</v>
       </c>
@@ -6602,13 +6575,13 @@
         <v>42</v>
       </c>
       <c r="D357">
-        <v>2526</v>
+        <v>2711</v>
       </c>
       <c r="E357">
-        <v>2135</v>
-      </c>
-    </row>
-    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
       <c r="A358" t="s">
         <v>7</v>
       </c>
@@ -6619,13 +6592,13 @@
         <v>42</v>
       </c>
       <c r="D358">
-        <v>4262</v>
+        <v>4679</v>
       </c>
       <c r="E358">
-        <v>3287</v>
-      </c>
-    </row>
-    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
       <c r="A359" t="s">
         <v>7</v>
       </c>
@@ -6636,13 +6609,13 @@
         <v>43</v>
       </c>
       <c r="D359">
-        <v>30386</v>
+        <v>32738</v>
       </c>
       <c r="E359">
-        <v>12462</v>
-      </c>
-    </row>
-    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>13155</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
       <c r="A360" t="s">
         <v>7</v>
       </c>
@@ -6653,13 +6626,13 @@
         <v>43</v>
       </c>
       <c r="D360">
-        <v>159777</v>
+        <v>168120</v>
       </c>
       <c r="E360">
-        <v>62808</v>
-      </c>
-    </row>
-    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>65402</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
       <c r="A361" t="s">
         <v>7</v>
       </c>
@@ -6670,13 +6643,13 @@
         <v>43</v>
       </c>
       <c r="D361">
-        <v>3625</v>
+        <v>3938</v>
       </c>
       <c r="E361">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
       <c r="A362" t="s">
         <v>7</v>
       </c>
@@ -6687,13 +6660,13 @@
         <v>43</v>
       </c>
       <c r="D362">
-        <v>1279</v>
+        <v>1404</v>
       </c>
       <c r="E362">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
       <c r="A363" t="s">
         <v>7</v>
       </c>
@@ -6704,13 +6677,13 @@
         <v>43</v>
       </c>
       <c r="D363">
-        <v>7687</v>
+        <v>8511</v>
       </c>
       <c r="E363">
-        <v>4075</v>
-      </c>
-    </row>
-    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4394</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
       <c r="A364" t="s">
         <v>7</v>
       </c>
@@ -6721,13 +6694,13 @@
         <v>43</v>
       </c>
       <c r="D364">
-        <v>2302</v>
+        <v>2516</v>
       </c>
       <c r="E364">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
       <c r="A365" t="s">
         <v>7</v>
       </c>
@@ -6738,13 +6711,13 @@
         <v>43</v>
       </c>
       <c r="D365">
-        <v>41893</v>
+        <v>44723</v>
       </c>
       <c r="E365">
-        <v>15794</v>
-      </c>
-    </row>
-    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>16533</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
       <c r="A366" t="s">
         <v>7</v>
       </c>
@@ -6755,13 +6728,13 @@
         <v>43</v>
       </c>
       <c r="D366">
-        <v>18126</v>
+        <v>19551</v>
       </c>
       <c r="E366">
-        <v>7683</v>
-      </c>
-    </row>
-    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>8047</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
       <c r="A367" t="s">
         <v>7</v>
       </c>
@@ -6772,13 +6745,13 @@
         <v>43</v>
       </c>
       <c r="D367">
-        <v>52987</v>
+        <v>57275</v>
       </c>
       <c r="E367">
-        <v>17245</v>
-      </c>
-    </row>
-    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>18078</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
       <c r="A368" t="s">
         <v>7</v>
       </c>
@@ -6789,13 +6762,13 @@
         <v>43</v>
       </c>
       <c r="D368">
-        <v>16796</v>
+        <v>17875</v>
       </c>
       <c r="E368">
-        <v>7205</v>
-      </c>
-    </row>
-    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7532</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
       <c r="A369" t="s">
         <v>7</v>
       </c>
@@ -6806,13 +6779,13 @@
         <v>43</v>
       </c>
       <c r="D369">
-        <v>23798</v>
+        <v>25641</v>
       </c>
       <c r="E369">
-        <v>11935</v>
-      </c>
-    </row>
-    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>12683</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
       <c r="A370" t="s">
         <v>7</v>
       </c>
@@ -6823,13 +6796,13 @@
         <v>43</v>
       </c>
       <c r="D370">
-        <v>916</v>
+        <v>1028</v>
       </c>
       <c r="E370">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
       <c r="A371" t="s">
         <v>7</v>
       </c>
@@ -6840,13 +6813,13 @@
         <v>43</v>
       </c>
       <c r="D371">
-        <v>10962</v>
+        <v>11947</v>
       </c>
       <c r="E371">
-        <v>5796</v>
-      </c>
-    </row>
-    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6111</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
       <c r="A372" t="s">
         <v>7</v>
       </c>
@@ -6857,13 +6830,13 @@
         <v>43</v>
       </c>
       <c r="D372">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E372">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
       <c r="A373" t="s">
         <v>7</v>
       </c>
@@ -6874,13 +6847,13 @@
         <v>43</v>
       </c>
       <c r="D373">
-        <v>2781</v>
+        <v>2949</v>
       </c>
       <c r="E373">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="374" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
       <c r="A374" t="s">
         <v>7</v>
       </c>
@@ -6891,13 +6864,13 @@
         <v>43</v>
       </c>
       <c r="D374">
-        <v>1258</v>
+        <v>1317</v>
       </c>
       <c r="E374">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
       <c r="A375" t="s">
         <v>7</v>
       </c>
@@ -6908,13 +6881,13 @@
         <v>43</v>
       </c>
       <c r="D375">
-        <v>89802</v>
+        <v>101841</v>
       </c>
       <c r="E375">
-        <v>33495</v>
-      </c>
-    </row>
-    <row r="376" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>37347</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
       <c r="A376" t="s">
         <v>7</v>
       </c>
@@ -6925,13 +6898,13 @@
         <v>43</v>
       </c>
       <c r="D376">
-        <v>8518</v>
+        <v>9479</v>
       </c>
       <c r="E376">
-        <v>2290</v>
-      </c>
-    </row>
-    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
       <c r="A377" t="s">
         <v>7</v>
       </c>
@@ -6942,13 +6915,13 @@
         <v>43</v>
       </c>
       <c r="D377">
-        <v>18068</v>
+        <v>18875</v>
       </c>
       <c r="E377">
-        <v>7134</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7417</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
       <c r="A378" t="s">
         <v>7</v>
       </c>
@@ -6959,13 +6932,13 @@
         <v>43</v>
       </c>
       <c r="D378">
-        <v>49283</v>
+        <v>52572</v>
       </c>
       <c r="E378">
-        <v>22589</v>
-      </c>
-    </row>
-    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>23644</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
       <c r="A379" t="s">
         <v>7</v>
       </c>
@@ -6976,30 +6949,30 @@
         <v>43</v>
       </c>
       <c r="D379">
-        <v>35190</v>
+        <v>38232</v>
       </c>
       <c r="E379">
-        <v>17031</v>
-      </c>
-    </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A380" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B380" s="2" t="s">
+        <v>18051</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" t="s">
+        <v>7</v>
+      </c>
+      <c r="B380" t="s">
         <v>32</v>
       </c>
-      <c r="C380" s="2" t="s">
+      <c r="C380" t="s">
         <v>43</v>
       </c>
-      <c r="D380" s="3">
-        <v>30372</v>
-      </c>
-      <c r="E380" s="3">
-        <v>11531</v>
-      </c>
-    </row>
-    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D380">
+        <v>33316</v>
+      </c>
+      <c r="E380">
+        <v>12189</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
       <c r="A381" t="s">
         <v>7</v>
       </c>
@@ -7010,13 +6983,13 @@
         <v>43</v>
       </c>
       <c r="D381">
-        <v>71957</v>
+        <v>85586</v>
       </c>
       <c r="E381">
-        <v>26156</v>
-      </c>
-    </row>
-    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>28588</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
       <c r="A382" t="s">
         <v>7</v>
       </c>
@@ -7027,13 +7000,13 @@
         <v>43</v>
       </c>
       <c r="D382">
-        <v>8426</v>
+        <v>9003</v>
       </c>
       <c r="E382">
-        <v>4182</v>
-      </c>
-    </row>
-    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4386</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
       <c r="A383" t="s">
         <v>7</v>
       </c>
@@ -7044,13 +7017,13 @@
         <v>43</v>
       </c>
       <c r="D383">
-        <v>7157</v>
+        <v>7760</v>
       </c>
       <c r="E383">
-        <v>3017</v>
-      </c>
-    </row>
-    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
       <c r="A384" t="s">
         <v>7</v>
       </c>
@@ -7061,13 +7034,13 @@
         <v>43</v>
       </c>
       <c r="D384">
-        <v>25359</v>
+        <v>27234</v>
       </c>
       <c r="E384">
-        <v>9831</v>
-      </c>
-    </row>
-    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>10257</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
       <c r="A385" t="s">
         <v>7</v>
       </c>
@@ -7078,13 +7051,13 @@
         <v>43</v>
       </c>
       <c r="D385">
-        <v>12797</v>
+        <v>13839</v>
       </c>
       <c r="E385">
-        <v>5538</v>
-      </c>
-    </row>
-    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>5820</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
       <c r="A386" t="s">
         <v>7</v>
       </c>
@@ -7095,13 +7068,13 @@
         <v>43</v>
       </c>
       <c r="D386">
-        <v>19023</v>
+        <v>20469</v>
       </c>
       <c r="E386">
-        <v>7711</v>
-      </c>
-    </row>
-    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>8136</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
       <c r="A387" t="s">
         <v>7</v>
       </c>
@@ -7112,13 +7085,13 @@
         <v>44</v>
       </c>
       <c r="D387">
-        <v>265126</v>
+        <v>285378</v>
       </c>
       <c r="E387">
-        <v>100591</v>
-      </c>
-    </row>
-    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>104908</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
       <c r="A388" t="s">
         <v>7</v>
       </c>
@@ -7129,13 +7102,13 @@
         <v>44</v>
       </c>
       <c r="D388">
-        <v>796320</v>
+        <v>858254</v>
       </c>
       <c r="E388">
-        <v>306494</v>
-      </c>
-    </row>
-    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>321814</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
       <c r="A389" t="s">
         <v>7</v>
       </c>
@@ -7146,13 +7119,13 @@
         <v>44</v>
       </c>
       <c r="D389">
-        <v>77167</v>
+        <v>82336</v>
       </c>
       <c r="E389">
-        <v>24614</v>
-      </c>
-    </row>
-    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>25903</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5">
       <c r="A390" t="s">
         <v>7</v>
       </c>
@@ -7163,13 +7136,13 @@
         <v>44</v>
       </c>
       <c r="D390">
-        <v>7061</v>
+        <v>7344</v>
       </c>
       <c r="E390">
-        <v>3635</v>
-      </c>
-    </row>
-    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5">
       <c r="A391" t="s">
         <v>7</v>
       </c>
@@ -7180,13 +7153,13 @@
         <v>44</v>
       </c>
       <c r="D391">
-        <v>13262</v>
+        <v>14539</v>
       </c>
       <c r="E391">
-        <v>5750</v>
-      </c>
-    </row>
-    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6008</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5">
       <c r="A392" t="s">
         <v>7</v>
       </c>
@@ -7197,13 +7170,13 @@
         <v>44</v>
       </c>
       <c r="D392">
-        <v>15983</v>
+        <v>17165</v>
       </c>
       <c r="E392">
-        <v>7281</v>
-      </c>
-    </row>
-    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7649</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5">
       <c r="A393" t="s">
         <v>7</v>
       </c>
@@ -7214,13 +7187,13 @@
         <v>44</v>
       </c>
       <c r="D393">
-        <v>70928</v>
+        <v>75851</v>
       </c>
       <c r="E393">
-        <v>24072</v>
-      </c>
-    </row>
-    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>25114</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5">
       <c r="A394" t="s">
         <v>7</v>
       </c>
@@ -7231,13 +7204,13 @@
         <v>44</v>
       </c>
       <c r="D394">
-        <v>49696</v>
+        <v>54103</v>
       </c>
       <c r="E394">
-        <v>22899</v>
-      </c>
-    </row>
-    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>24003</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5">
       <c r="A395" t="s">
         <v>7</v>
       </c>
@@ -7248,13 +7221,13 @@
         <v>44</v>
       </c>
       <c r="D395">
-        <v>269709</v>
+        <v>289101</v>
       </c>
       <c r="E395">
-        <v>94002</v>
-      </c>
-    </row>
-    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>97522</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5">
       <c r="A396" t="s">
         <v>7</v>
       </c>
@@ -7265,13 +7238,13 @@
         <v>44</v>
       </c>
       <c r="D396">
-        <v>4212</v>
+        <v>4898</v>
       </c>
       <c r="E396">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5">
       <c r="A397" t="s">
         <v>7</v>
       </c>
@@ -7282,13 +7255,13 @@
         <v>44</v>
       </c>
       <c r="D397">
-        <v>15037</v>
+        <v>16550</v>
       </c>
       <c r="E397">
-        <v>7180</v>
-      </c>
-    </row>
-    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7581</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5">
       <c r="A398" t="s">
         <v>7</v>
       </c>
@@ -7299,13 +7272,13 @@
         <v>44</v>
       </c>
       <c r="D398">
-        <v>129007</v>
+        <v>137756</v>
       </c>
       <c r="E398">
-        <v>50376</v>
-      </c>
-    </row>
-    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>52381</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5">
       <c r="A399" t="s">
         <v>7</v>
       </c>
@@ -7316,13 +7289,13 @@
         <v>44</v>
       </c>
       <c r="D399">
-        <v>298811</v>
+        <v>316512</v>
       </c>
       <c r="E399">
-        <v>81686</v>
-      </c>
-    </row>
-    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>84716</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
       <c r="A400" t="s">
         <v>7</v>
       </c>
@@ -7333,13 +7306,13 @@
         <v>44</v>
       </c>
       <c r="D400">
-        <v>249773</v>
+        <v>266721</v>
       </c>
       <c r="E400">
-        <v>95590</v>
-      </c>
-    </row>
-    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>99209</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
       <c r="A401" t="s">
         <v>7</v>
       </c>
@@ -7350,13 +7323,13 @@
         <v>44</v>
       </c>
       <c r="D401">
-        <v>399692</v>
+        <v>424156</v>
       </c>
       <c r="E401">
-        <v>131643</v>
-      </c>
-    </row>
-    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>135869</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5">
       <c r="A402" t="s">
         <v>7</v>
       </c>
@@ -7367,13 +7340,13 @@
         <v>44</v>
       </c>
       <c r="D402">
-        <v>19188</v>
+        <v>20484</v>
       </c>
       <c r="E402">
-        <v>6266</v>
-      </c>
-    </row>
-    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6505</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
       <c r="A403" t="s">
         <v>7</v>
       </c>
@@ -7384,13 +7357,13 @@
         <v>44</v>
       </c>
       <c r="D403">
-        <v>253439</v>
+        <v>270227</v>
       </c>
       <c r="E403">
-        <v>104321</v>
-      </c>
-    </row>
-    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>108336</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
       <c r="A404" t="s">
         <v>7</v>
       </c>
@@ -7401,13 +7374,13 @@
         <v>44</v>
       </c>
       <c r="D404">
-        <v>46794</v>
+        <v>48913</v>
       </c>
       <c r="E404">
-        <v>21948</v>
-      </c>
-    </row>
-    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>22494</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
       <c r="A405" t="s">
         <v>7</v>
       </c>
@@ -7418,13 +7391,13 @@
         <v>44</v>
       </c>
       <c r="D405">
-        <v>30198</v>
+        <v>31933</v>
       </c>
       <c r="E405">
-        <v>9995</v>
-      </c>
-    </row>
-    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>10349</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
       <c r="A406" t="s">
         <v>7</v>
       </c>
@@ -7435,13 +7408,13 @@
         <v>44</v>
       </c>
       <c r="D406">
-        <v>20788</v>
+        <v>22404</v>
       </c>
       <c r="E406">
-        <v>10008</v>
-      </c>
-    </row>
-    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>10489</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5">
       <c r="A407" t="s">
         <v>7</v>
       </c>
@@ -7452,13 +7425,13 @@
         <v>44</v>
       </c>
       <c r="D407">
-        <v>608543</v>
+        <v>655586</v>
       </c>
       <c r="E407">
-        <v>195585</v>
-      </c>
-    </row>
-    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>204107</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
       <c r="A408" t="s">
         <v>7</v>
       </c>
@@ -7469,13 +7442,13 @@
         <v>44</v>
       </c>
       <c r="D408">
-        <v>12365</v>
+        <v>13211</v>
       </c>
       <c r="E408">
-        <v>5751</v>
-      </c>
-    </row>
-    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>6036</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
       <c r="A409" t="s">
         <v>7</v>
       </c>
@@ -7486,13 +7459,13 @@
         <v>44</v>
       </c>
       <c r="D409">
-        <v>188470</v>
+        <v>202913</v>
       </c>
       <c r="E409">
-        <v>65569</v>
-      </c>
-    </row>
-    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>68192</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
       <c r="A410" t="s">
         <v>7</v>
       </c>
@@ -7503,13 +7476,13 @@
         <v>44</v>
       </c>
       <c r="D410">
-        <v>182111</v>
+        <v>194098</v>
       </c>
       <c r="E410">
-        <v>73613</v>
-      </c>
-    </row>
-    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>76717</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
       <c r="A411" t="s">
         <v>7</v>
       </c>
@@ -7520,30 +7493,30 @@
         <v>44</v>
       </c>
       <c r="D411">
-        <v>548758</v>
+        <v>581881</v>
       </c>
       <c r="E411">
-        <v>184528</v>
-      </c>
-    </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A412" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B412" s="2" t="s">
+        <v>191330</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" t="s">
+        <v>7</v>
+      </c>
+      <c r="B412" t="s">
         <v>32</v>
       </c>
-      <c r="C412" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D412" s="3">
-        <v>187264</v>
-      </c>
-      <c r="E412" s="3">
-        <v>68778</v>
-      </c>
-    </row>
-    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C412" t="s">
+        <v>44</v>
+      </c>
+      <c r="D412">
+        <v>202644</v>
+      </c>
+      <c r="E412">
+        <v>72570</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
       <c r="A413" t="s">
         <v>7</v>
       </c>
@@ -7554,13 +7527,13 @@
         <v>44</v>
       </c>
       <c r="D413">
-        <v>135719</v>
+        <v>146599</v>
       </c>
       <c r="E413">
-        <v>44145</v>
-      </c>
-    </row>
-    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
       <c r="A414" t="s">
         <v>7</v>
       </c>
@@ -7571,13 +7544,13 @@
         <v>44</v>
       </c>
       <c r="D414">
-        <v>215424</v>
+        <v>229370</v>
       </c>
       <c r="E414">
-        <v>83370</v>
-      </c>
-    </row>
-    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>86307</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
       <c r="A415" t="s">
         <v>7</v>
       </c>
@@ -7588,13 +7561,13 @@
         <v>44</v>
       </c>
       <c r="D415">
-        <v>14462</v>
+        <v>15379</v>
       </c>
       <c r="E415">
-        <v>7622</v>
-      </c>
-    </row>
-    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7957</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
       <c r="A416" t="s">
         <v>7</v>
       </c>
@@ -7605,13 +7578,13 @@
         <v>44</v>
       </c>
       <c r="D416">
-        <v>137181</v>
+        <v>147595</v>
       </c>
       <c r="E416">
-        <v>45262</v>
-      </c>
-    </row>
-    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>47417</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
       <c r="A417" t="s">
         <v>7</v>
       </c>
@@ -7622,13 +7595,13 @@
         <v>44</v>
       </c>
       <c r="D417">
-        <v>129691</v>
+        <v>138750</v>
       </c>
       <c r="E417">
-        <v>52294</v>
-      </c>
-    </row>
-    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>54491</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
       <c r="A418" t="s">
         <v>7</v>
       </c>
@@ -7639,13 +7612,13 @@
         <v>44</v>
       </c>
       <c r="D418">
-        <v>317143</v>
+        <v>338972</v>
       </c>
       <c r="E418">
-        <v>96695</v>
-      </c>
-    </row>
-    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>100425</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5">
       <c r="A419" t="s">
         <v>7</v>
       </c>
@@ -7656,13 +7629,13 @@
         <v>45</v>
       </c>
       <c r="D419">
-        <v>1064</v>
+        <v>1120</v>
       </c>
       <c r="E419">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5">
       <c r="A420" t="s">
         <v>7</v>
       </c>
@@ -7673,13 +7646,13 @@
         <v>45</v>
       </c>
       <c r="D420">
-        <v>21699</v>
+        <v>23581</v>
       </c>
       <c r="E420">
-        <v>12955</v>
-      </c>
-    </row>
-    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>13989</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5">
       <c r="A421" t="s">
         <v>7</v>
       </c>
@@ -7690,13 +7663,13 @@
         <v>45</v>
       </c>
       <c r="D421">
-        <v>1169</v>
+        <v>1284</v>
       </c>
       <c r="E421">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5">
       <c r="A422" t="s">
         <v>7</v>
       </c>
@@ -7707,13 +7680,13 @@
         <v>45</v>
       </c>
       <c r="D422">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E422">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
       <c r="A423" t="s">
         <v>7</v>
       </c>
@@ -7724,13 +7697,13 @@
         <v>45</v>
       </c>
       <c r="D423">
-        <v>968</v>
+        <v>1036</v>
       </c>
       <c r="E423">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="424" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5">
       <c r="A424" t="s">
         <v>7</v>
       </c>
@@ -7741,13 +7714,13 @@
         <v>45</v>
       </c>
       <c r="D424">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E424">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5">
       <c r="A425" t="s">
         <v>7</v>
       </c>
@@ -7758,13 +7731,13 @@
         <v>45</v>
       </c>
       <c r="D425">
-        <v>4295</v>
+        <v>4562</v>
       </c>
       <c r="E425">
-        <v>2977</v>
-      </c>
-    </row>
-    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>3162</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5">
       <c r="A426" t="s">
         <v>7</v>
       </c>
@@ -7781,7 +7754,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:5">
       <c r="A427" t="s">
         <v>7</v>
       </c>
@@ -7798,7 +7771,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:5">
       <c r="A428" t="s">
         <v>7</v>
       </c>
@@ -7809,13 +7782,13 @@
         <v>45</v>
       </c>
       <c r="D428">
-        <v>3868</v>
+        <v>4221</v>
       </c>
       <c r="E428">
-        <v>2684</v>
-      </c>
-    </row>
-    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2935</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5">
       <c r="A429" t="s">
         <v>7</v>
       </c>
@@ -7826,13 +7799,13 @@
         <v>45</v>
       </c>
       <c r="D429">
-        <v>7075</v>
+        <v>7292</v>
       </c>
       <c r="E429">
-        <v>4829</v>
-      </c>
-    </row>
-    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4986</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5">
       <c r="A430" t="s">
         <v>7</v>
       </c>
@@ -7843,13 +7816,13 @@
         <v>45</v>
       </c>
       <c r="D430">
-        <v>1969</v>
+        <v>2088</v>
       </c>
       <c r="E430">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5">
       <c r="A431" t="s">
         <v>7</v>
       </c>
@@ -7860,13 +7833,13 @@
         <v>45</v>
       </c>
       <c r="D431">
-        <v>2777</v>
+        <v>3028</v>
       </c>
       <c r="E431">
-        <v>2108</v>
-      </c>
-    </row>
-    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5">
       <c r="A432" t="s">
         <v>7</v>
       </c>
@@ -7883,7 +7856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:5">
       <c r="A433" t="s">
         <v>7</v>
       </c>
@@ -7894,13 +7867,13 @@
         <v>45</v>
       </c>
       <c r="D433">
-        <v>1621</v>
+        <v>1776</v>
       </c>
       <c r="E433">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5">
       <c r="A434" t="s">
         <v>7</v>
       </c>
@@ -7911,13 +7884,13 @@
         <v>45</v>
       </c>
       <c r="D434">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E434">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5">
       <c r="A435" t="s">
         <v>7</v>
       </c>
@@ -7928,13 +7901,13 @@
         <v>45</v>
       </c>
       <c r="D435">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="E435">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5">
       <c r="A436" t="s">
         <v>7</v>
       </c>
@@ -7951,7 +7924,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:5">
       <c r="A437" t="s">
         <v>7</v>
       </c>
@@ -7962,13 +7935,13 @@
         <v>45</v>
       </c>
       <c r="D437">
-        <v>10379</v>
+        <v>11335</v>
       </c>
       <c r="E437">
-        <v>6780</v>
-      </c>
-    </row>
-    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>7322</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5">
       <c r="A438" t="s">
         <v>7</v>
       </c>
@@ -7979,13 +7952,13 @@
         <v>45</v>
       </c>
       <c r="D438">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E438">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5">
       <c r="A439" t="s">
         <v>7</v>
       </c>
@@ -7996,13 +7969,13 @@
         <v>45</v>
       </c>
       <c r="D439">
-        <v>1113</v>
+        <v>1237</v>
       </c>
       <c r="E439">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5">
       <c r="A440" t="s">
         <v>7</v>
       </c>
@@ -8013,13 +7986,13 @@
         <v>45</v>
       </c>
       <c r="D440">
-        <v>7501</v>
+        <v>8054</v>
       </c>
       <c r="E440">
-        <v>5262</v>
-      </c>
-    </row>
-    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>5641</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5">
       <c r="A441" t="s">
         <v>7</v>
       </c>
@@ -8030,30 +8003,30 @@
         <v>45</v>
       </c>
       <c r="D441">
-        <v>4407</v>
+        <v>4586</v>
       </c>
       <c r="E441">
-        <v>3050</v>
-      </c>
-    </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A442" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B442" s="2" t="s">
+        <v>3163</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" t="s">
+        <v>7</v>
+      </c>
+      <c r="B442" t="s">
         <v>32</v>
       </c>
-      <c r="C442" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D442" s="3">
-        <v>3806</v>
-      </c>
-      <c r="E442" s="3">
-        <v>2520</v>
-      </c>
-    </row>
-    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C442" t="s">
+        <v>45</v>
+      </c>
+      <c r="D442">
+        <v>4222</v>
+      </c>
+      <c r="E442">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5">
       <c r="A443" t="s">
         <v>7</v>
       </c>
@@ -8064,13 +8037,13 @@
         <v>45</v>
       </c>
       <c r="D443">
-        <v>4781</v>
+        <v>5672</v>
       </c>
       <c r="E443">
-        <v>3862</v>
-      </c>
-    </row>
-    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4467</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5">
       <c r="A444" t="s">
         <v>7</v>
       </c>
@@ -8081,13 +8054,13 @@
         <v>45</v>
       </c>
       <c r="D444">
-        <v>945</v>
+        <v>1005</v>
       </c>
       <c r="E444">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5">
       <c r="A445" t="s">
         <v>7</v>
       </c>
@@ -8098,13 +8071,13 @@
         <v>45</v>
       </c>
       <c r="D445">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="E445">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5">
       <c r="A446" t="s">
         <v>7</v>
       </c>
@@ -8115,13 +8088,13 @@
         <v>45</v>
       </c>
       <c r="D446">
-        <v>2166</v>
+        <v>2339</v>
       </c>
       <c r="E446">
-        <v>1670</v>
-      </c>
-    </row>
-    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5">
       <c r="A447" t="s">
         <v>7</v>
       </c>
@@ -8132,13 +8105,13 @@
         <v>45</v>
       </c>
       <c r="D447">
-        <v>1358</v>
+        <v>1461</v>
       </c>
       <c r="E447">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5">
       <c r="A448" t="s">
         <v>7</v>
       </c>
@@ -8149,13 +8122,13 @@
         <v>45</v>
       </c>
       <c r="D448">
-        <v>2620</v>
+        <v>2893</v>
       </c>
       <c r="E448">
-        <v>1963</v>
-      </c>
-    </row>
-    <row r="449" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="449" spans="2:5">
       <c r="B449" t="s">
         <v>8</v>
       </c>
@@ -8166,7 +8139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="2:5">
       <c r="B450" t="s">
         <v>9</v>
       </c>
@@ -8177,7 +8150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="2:5">
       <c r="B451" t="s">
         <v>11</v>
       </c>
@@ -8188,9 +8161,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="2:5">
       <c r="B452" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D452">
         <v>0</v>
@@ -8199,9 +8172,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="2:5">
       <c r="B453" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D453">
         <v>0</v>
@@ -8210,9 +8183,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="2:5">
       <c r="B454" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D454">
         <v>0</v>
@@ -8221,9 +8194,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="2:5">
       <c r="B455" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D455">
         <v>0</v>
@@ -8232,9 +8205,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="2:5">
       <c r="B456" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D456">
         <v>0</v>
@@ -8243,9 +8216,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="2:5">
       <c r="B457" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D457">
         <v>0</v>
@@ -8254,9 +8227,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="2:5">
       <c r="B458" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D458">
         <v>0</v>
@@ -8265,9 +8238,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="2:5">
       <c r="B459" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D459">
         <v>0</v>
@@ -8276,9 +8249,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="2:5">
       <c r="B460" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D460">
         <v>0</v>
@@ -8287,9 +8260,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="2:5">
       <c r="B461" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D461">
         <v>0</v>
@@ -8298,20 +8271,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="462" spans="2:5">
       <c r="B462" t="s">
-        <v>32</v>
-      </c>
-      <c r="D462" s="1">
+        <v>33</v>
+      </c>
+      <c r="D462">
         <v>0</v>
       </c>
-      <c r="E462" s="1">
+      <c r="E462">
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="2:5">
       <c r="B463" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D463">
         <v>0</v>
@@ -8320,284 +8293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="2:5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B464" t="s">
-        <v>35</v>
-      </c>
-      <c r="D464">
-        <v>0</v>
-      </c>
-      <c r="E464">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E464" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Plan de Justicia del Pueblo P'urhépecha"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ecbbb845-5bb4-49a6-a031-2c6210f1a021">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2311af43-dfdb-495f-8272-1d5374a07a4f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010086ADF0657346C74FA4159949F83B0105" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e679190041f368e5f1999762c1635bea">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ecbbb845-5bb4-49a6-a031-2c6210f1a021" xmlns:ns3="2311af43-dfdb-495f-8272-1d5374a07a4f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="106f98ec6a760573afb5fafd9fd455c8" ns2:_="" ns3:_="">
-    <xsd:import namespace="ecbbb845-5bb4-49a6-a031-2c6210f1a021"/>
-    <xsd:import namespace="2311af43-dfdb-495f-8272-1d5374a07a4f"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ecbbb845-5bb4-49a6-a031-2c6210f1a021" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6c7de3c9-8e68-46a6-abfc-7512e1ae618b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2311af43-dfdb-495f-8272-1d5374a07a4f" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{57b665d3-a353-4c8b-994f-ed147fe15c37}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="2311af43-dfdb-495f-8272-1d5374a07a4f">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2837CAB3-BD1C-4BEA-B86C-C61B139133C0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83E93B8A-D666-4A38-9258-3D7286E90443}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ecbbb845-5bb4-49a6-a031-2c6210f1a021"/>
-    <ds:schemaRef ds:uri="2311af43-dfdb-495f-8272-1d5374a07a4f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A90262F-55A6-43CB-ACA6-E85AC1EEB311}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ecbbb845-5bb4-49a6-a031-2c6210f1a021"/>
-    <ds:schemaRef ds:uri="2311af43-dfdb-495f-8272-1d5374a07a4f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/plan_justicia/procedimientos_personas_plan_justicia.xlsx
+++ b/data/plan_justicia/procedimientos_personas_plan_justicia.xlsx
@@ -8296,4 +8296,237 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010086ADF0657346C74FA4159949F83B0105" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e679190041f368e5f1999762c1635bea">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ecbbb845-5bb4-49a6-a031-2c6210f1a021" xmlns:ns3="2311af43-dfdb-495f-8272-1d5374a07a4f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="106f98ec6a760573afb5fafd9fd455c8" ns2:_="" ns3:_="">
+    <xsd:import namespace="ecbbb845-5bb4-49a6-a031-2c6210f1a021"/>
+    <xsd:import namespace="2311af43-dfdb-495f-8272-1d5374a07a4f"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ecbbb845-5bb4-49a6-a031-2c6210f1a021" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6c7de3c9-8e68-46a6-abfc-7512e1ae618b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2311af43-dfdb-495f-8272-1d5374a07a4f" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{57b665d3-a353-4c8b-994f-ed147fe15c37}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="2311af43-dfdb-495f-8272-1d5374a07a4f">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ecbbb845-5bb4-49a6-a031-2c6210f1a021">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2311af43-dfdb-495f-8272-1d5374a07a4f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75257A69-6152-4A89-93E6-E51B4BFD37F7}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{288033A1-A5D8-42D3-BFCE-5052E2F3A545}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{406EB8AD-A6A0-4E94-BDB4-A794ED08FE64}"/>
 </file>
--- a/data/plan_justicia/procedimientos_personas_plan_justicia.xlsx
+++ b/data/plan_justicia/procedimientos_personas_plan_justicia.xlsx
@@ -8520,13 +8520,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75257A69-6152-4A89-93E6-E51B4BFD37F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD379BE9-59A2-4BD2-B90F-6064CE541D39}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{288033A1-A5D8-42D3-BFCE-5052E2F3A545}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{988D3428-02A1-4E2C-AD38-21D0C25896C3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{406EB8AD-A6A0-4E94-BDB4-A794ED08FE64}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAE36736-B061-43C9-B2C0-38CE9C0E09D1}"/>
 </file>
--- a/data/plan_justicia/procedimientos_personas_plan_justicia.xlsx
+++ b/data/plan_justicia/procedimientos_personas_plan_justicia.xlsx
@@ -8520,13 +8520,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD379BE9-59A2-4BD2-B90F-6064CE541D39}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B151228D-BDFE-4FCC-8F9E-A80657B2667D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{988D3428-02A1-4E2C-AD38-21D0C25896C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04F87B6C-E3DC-4795-86AB-8E61058B7CB1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAE36736-B061-43C9-B2C0-38CE9C0E09D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37E88904-1744-4031-AA59-EC44D4DA3F72}"/>
 </file>
--- a/data/plan_justicia/procedimientos_personas_plan_justicia.xlsx
+++ b/data/plan_justicia/procedimientos_personas_plan_justicia.xlsx
@@ -540,10 +540,10 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>174617</v>
+        <v>181283</v>
       </c>
       <c r="E2">
-        <v>73819</v>
+        <v>75640</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -557,10 +557,10 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>908482</v>
+        <v>946387</v>
       </c>
       <c r="E3">
-        <v>339689</v>
+        <v>349963</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -574,10 +574,10 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>54742</v>
+        <v>56833</v>
       </c>
       <c r="E4">
-        <v>16439</v>
+        <v>16892</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -591,10 +591,10 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>5819</v>
+        <v>5979</v>
       </c>
       <c r="E5">
-        <v>2846</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -625,7 +625,7 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>9936</v>
+        <v>9937</v>
       </c>
       <c r="E7">
         <v>4947</v>
@@ -642,10 +642,10 @@
         <v>41</v>
       </c>
       <c r="D8">
-        <v>37240</v>
+        <v>38662</v>
       </c>
       <c r="E8">
-        <v>14666</v>
+        <v>15144</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -676,10 +676,10 @@
         <v>41</v>
       </c>
       <c r="D10">
-        <v>171603</v>
+        <v>180379</v>
       </c>
       <c r="E10">
-        <v>64063</v>
+        <v>66193</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -693,10 +693,10 @@
         <v>41</v>
       </c>
       <c r="D11">
-        <v>3331</v>
+        <v>3397</v>
       </c>
       <c r="E11">
-        <v>1626</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -710,10 +710,10 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>13252</v>
+        <v>13486</v>
       </c>
       <c r="E12">
-        <v>6411</v>
+        <v>6479</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -727,10 +727,10 @@
         <v>41</v>
       </c>
       <c r="D13">
-        <v>131940</v>
+        <v>137582</v>
       </c>
       <c r="E13">
-        <v>50300</v>
+        <v>51675</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -744,10 +744,10 @@
         <v>41</v>
       </c>
       <c r="D14">
-        <v>226523</v>
+        <v>242731</v>
       </c>
       <c r="E14">
-        <v>86238</v>
+        <v>90457</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -761,10 +761,10 @@
         <v>41</v>
       </c>
       <c r="D15">
-        <v>157207</v>
+        <v>162407</v>
       </c>
       <c r="E15">
-        <v>66334</v>
+        <v>67907</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -778,10 +778,10 @@
         <v>41</v>
       </c>
       <c r="D16">
-        <v>246360</v>
+        <v>256225</v>
       </c>
       <c r="E16">
-        <v>89424</v>
+        <v>91910</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -795,10 +795,10 @@
         <v>41</v>
       </c>
       <c r="D17">
-        <v>208572</v>
+        <v>218334</v>
       </c>
       <c r="E17">
-        <v>91483</v>
+        <v>94249</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -812,10 +812,10 @@
         <v>41</v>
       </c>
       <c r="D18">
-        <v>42626</v>
+        <v>45908</v>
       </c>
       <c r="E18">
-        <v>20084</v>
+        <v>21175</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -829,10 +829,10 @@
         <v>41</v>
       </c>
       <c r="D19">
-        <v>24630</v>
+        <v>25134</v>
       </c>
       <c r="E19">
-        <v>9928</v>
+        <v>10059</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -846,10 +846,10 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>19542</v>
+        <v>19784</v>
       </c>
       <c r="E20">
-        <v>9635</v>
+        <v>9726</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -863,10 +863,10 @@
         <v>41</v>
       </c>
       <c r="D21">
-        <v>346336</v>
+        <v>353394</v>
       </c>
       <c r="E21">
-        <v>127258</v>
+        <v>129033</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -897,10 +897,10 @@
         <v>41</v>
       </c>
       <c r="D23">
-        <v>124722</v>
+        <v>129842</v>
       </c>
       <c r="E23">
-        <v>48162</v>
+        <v>49379</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -914,10 +914,10 @@
         <v>41</v>
       </c>
       <c r="D24">
-        <v>200167</v>
+        <v>206555</v>
       </c>
       <c r="E24">
-        <v>77455</v>
+        <v>79186</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -931,7 +931,7 @@
         <v>41</v>
       </c>
       <c r="D25">
-        <v>325636</v>
+        <v>325641</v>
       </c>
       <c r="E25">
         <v>117163</v>
@@ -948,10 +948,10 @@
         <v>41</v>
       </c>
       <c r="D26">
-        <v>197233</v>
+        <v>197269</v>
       </c>
       <c r="E26">
-        <v>76706</v>
+        <v>76725</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -965,10 +965,10 @@
         <v>41</v>
       </c>
       <c r="D27">
-        <v>111267</v>
+        <v>112318</v>
       </c>
       <c r="E27">
-        <v>31619</v>
+        <v>31744</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -982,10 +982,10 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>191694</v>
+        <v>199402</v>
       </c>
       <c r="E28">
-        <v>71200</v>
+        <v>73094</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -999,10 +999,10 @@
         <v>41</v>
       </c>
       <c r="D29">
-        <v>18006</v>
+        <v>18352</v>
       </c>
       <c r="E29">
-        <v>8528</v>
+        <v>8628</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1016,10 +1016,10 @@
         <v>41</v>
       </c>
       <c r="D30">
-        <v>2509</v>
+        <v>2646</v>
       </c>
       <c r="E30">
-        <v>935</v>
+        <v>999</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1033,10 +1033,10 @@
         <v>41</v>
       </c>
       <c r="D31">
-        <v>8256</v>
+        <v>8286</v>
       </c>
       <c r="E31">
-        <v>3577</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1050,10 +1050,10 @@
         <v>41</v>
       </c>
       <c r="D32">
-        <v>303152</v>
+        <v>306874</v>
       </c>
       <c r="E32">
-        <v>84901</v>
+        <v>85252</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1067,10 +1067,10 @@
         <v>42</v>
       </c>
       <c r="D33">
-        <v>1594</v>
+        <v>1641</v>
       </c>
       <c r="E33">
-        <v>1355</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1084,10 +1084,10 @@
         <v>42</v>
       </c>
       <c r="D34">
-        <v>36854</v>
+        <v>37904</v>
       </c>
       <c r="E34">
-        <v>27223</v>
+        <v>27951</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1101,10 +1101,10 @@
         <v>42</v>
       </c>
       <c r="D35">
-        <v>1475</v>
+        <v>1547</v>
       </c>
       <c r="E35">
-        <v>1161</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1118,10 +1118,10 @@
         <v>42</v>
       </c>
       <c r="D36">
-        <v>2079</v>
+        <v>2144</v>
       </c>
       <c r="E36">
-        <v>1732</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1152,10 +1152,10 @@
         <v>42</v>
       </c>
       <c r="D38">
-        <v>2639</v>
+        <v>2747</v>
       </c>
       <c r="E38">
-        <v>2212</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1169,10 +1169,10 @@
         <v>42</v>
       </c>
       <c r="D39">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E39">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1203,10 +1203,10 @@
         <v>42</v>
       </c>
       <c r="D41">
-        <v>5766</v>
+        <v>6143</v>
       </c>
       <c r="E41">
-        <v>4836</v>
+        <v>5149</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1220,10 +1220,10 @@
         <v>42</v>
       </c>
       <c r="D42">
-        <v>12333</v>
+        <v>12794</v>
       </c>
       <c r="E42">
-        <v>9202</v>
+        <v>9560</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1237,10 +1237,10 @@
         <v>42</v>
       </c>
       <c r="D43">
-        <v>1660</v>
+        <v>1738</v>
       </c>
       <c r="E43">
-        <v>1404</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1254,10 +1254,10 @@
         <v>42</v>
       </c>
       <c r="D44">
-        <v>7790</v>
+        <v>8125</v>
       </c>
       <c r="E44">
-        <v>6520</v>
+        <v>6806</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1288,10 +1288,10 @@
         <v>42</v>
       </c>
       <c r="D46">
-        <v>3025</v>
+        <v>3144</v>
       </c>
       <c r="E46">
-        <v>2702</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1322,10 +1322,10 @@
         <v>42</v>
       </c>
       <c r="D48">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="E48">
-        <v>400</v>
+        <v>416</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1356,10 +1356,10 @@
         <v>42</v>
       </c>
       <c r="D50">
-        <v>19645</v>
+        <v>20191</v>
       </c>
       <c r="E50">
-        <v>9784</v>
+        <v>10176</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1373,10 +1373,10 @@
         <v>42</v>
       </c>
       <c r="D51">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E51">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1390,10 +1390,10 @@
         <v>42</v>
       </c>
       <c r="D52">
-        <v>2064</v>
+        <v>2138</v>
       </c>
       <c r="E52">
-        <v>1896</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1407,10 +1407,10 @@
         <v>42</v>
       </c>
       <c r="D53">
-        <v>8824</v>
+        <v>9113</v>
       </c>
       <c r="E53">
-        <v>6662</v>
+        <v>6860</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1424,10 +1424,10 @@
         <v>42</v>
       </c>
       <c r="D54">
-        <v>8571</v>
+        <v>8837</v>
       </c>
       <c r="E54">
-        <v>6853</v>
+        <v>7063</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1441,10 +1441,10 @@
         <v>42</v>
       </c>
       <c r="D55">
-        <v>5999</v>
+        <v>6909</v>
       </c>
       <c r="E55">
-        <v>5175</v>
+        <v>5948</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1458,10 +1458,10 @@
         <v>42</v>
       </c>
       <c r="D56">
-        <v>26966</v>
+        <v>27110</v>
       </c>
       <c r="E56">
-        <v>8508</v>
+        <v>8608</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1475,10 +1475,10 @@
         <v>42</v>
       </c>
       <c r="D57">
-        <v>2269</v>
+        <v>2335</v>
       </c>
       <c r="E57">
-        <v>1989</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1509,10 +1509,10 @@
         <v>42</v>
       </c>
       <c r="D59">
-        <v>4466</v>
+        <v>4608</v>
       </c>
       <c r="E59">
-        <v>3185</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1526,10 +1526,10 @@
         <v>42</v>
       </c>
       <c r="D60">
-        <v>2887</v>
+        <v>2964</v>
       </c>
       <c r="E60">
-        <v>2366</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1543,10 +1543,10 @@
         <v>42</v>
       </c>
       <c r="D61">
-        <v>5553</v>
+        <v>5791</v>
       </c>
       <c r="E61">
-        <v>3922</v>
+        <v>4082</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1560,10 +1560,10 @@
         <v>43</v>
       </c>
       <c r="D62">
-        <v>5854</v>
+        <v>5938</v>
       </c>
       <c r="E62">
-        <v>2869</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1577,10 +1577,10 @@
         <v>43</v>
       </c>
       <c r="D63">
-        <v>92414</v>
+        <v>96085</v>
       </c>
       <c r="E63">
-        <v>42226</v>
+        <v>43482</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1594,10 +1594,10 @@
         <v>43</v>
       </c>
       <c r="D64">
-        <v>1351</v>
+        <v>1361</v>
       </c>
       <c r="E64">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1611,10 +1611,10 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>2116</v>
+        <v>2226</v>
       </c>
       <c r="E65">
-        <v>1107</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1645,10 +1645,10 @@
         <v>43</v>
       </c>
       <c r="D67">
-        <v>3727</v>
+        <v>3882</v>
       </c>
       <c r="E67">
-        <v>1675</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1696,10 +1696,10 @@
         <v>43</v>
       </c>
       <c r="D70">
-        <v>12352</v>
+        <v>12829</v>
       </c>
       <c r="E70">
-        <v>6008</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1713,10 +1713,10 @@
         <v>43</v>
       </c>
       <c r="D71">
-        <v>22831</v>
+        <v>23643</v>
       </c>
       <c r="E71">
-        <v>11097</v>
+        <v>11511</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1730,10 +1730,10 @@
         <v>43</v>
       </c>
       <c r="D72">
-        <v>1849</v>
+        <v>1907</v>
       </c>
       <c r="E72">
-        <v>1017</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1747,10 +1747,10 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>9689</v>
+        <v>10296</v>
       </c>
       <c r="E73">
-        <v>4908</v>
+        <v>5173</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1764,10 +1764,10 @@
         <v>43</v>
       </c>
       <c r="D74">
-        <v>8967</v>
+        <v>9436</v>
       </c>
       <c r="E74">
-        <v>4601</v>
+        <v>4761</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1781,10 +1781,10 @@
         <v>43</v>
       </c>
       <c r="D75">
-        <v>1588</v>
+        <v>1608</v>
       </c>
       <c r="E75">
-        <v>1072</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1798,10 +1798,10 @@
         <v>43</v>
       </c>
       <c r="D76">
-        <v>1217</v>
+        <v>1254</v>
       </c>
       <c r="E76">
-        <v>641</v>
+        <v>651</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1815,10 +1815,10 @@
         <v>43</v>
       </c>
       <c r="D77">
-        <v>56403</v>
+        <v>56835</v>
       </c>
       <c r="E77">
-        <v>21501</v>
+        <v>21664</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1849,10 +1849,10 @@
         <v>43</v>
       </c>
       <c r="D79">
-        <v>2865</v>
+        <v>2971</v>
       </c>
       <c r="E79">
-        <v>1537</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1866,10 +1866,10 @@
         <v>43</v>
       </c>
       <c r="D80">
-        <v>43659</v>
+        <v>45262</v>
       </c>
       <c r="E80">
-        <v>20414</v>
+        <v>20985</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1917,10 +1917,10 @@
         <v>43</v>
       </c>
       <c r="D83">
-        <v>72922</v>
+        <v>73086</v>
       </c>
       <c r="E83">
-        <v>25314</v>
+        <v>25380</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -1934,10 +1934,10 @@
         <v>43</v>
       </c>
       <c r="D84">
-        <v>5058</v>
+        <v>5253</v>
       </c>
       <c r="E84">
-        <v>2606</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -1951,10 +1951,10 @@
         <v>43</v>
       </c>
       <c r="D85">
-        <v>5390</v>
+        <v>5580</v>
       </c>
       <c r="E85">
-        <v>2917</v>
+        <v>2987</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -1985,10 +1985,10 @@
         <v>43</v>
       </c>
       <c r="D87">
-        <v>10379</v>
+        <v>10586</v>
       </c>
       <c r="E87">
-        <v>5382</v>
+        <v>5478</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2002,10 +2002,10 @@
         <v>44</v>
       </c>
       <c r="D88">
-        <v>168763</v>
+        <v>175345</v>
       </c>
       <c r="E88">
-        <v>72554</v>
+        <v>74388</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2019,10 +2019,10 @@
         <v>44</v>
       </c>
       <c r="D89">
-        <v>816068</v>
+        <v>850302</v>
       </c>
       <c r="E89">
-        <v>321562</v>
+        <v>331460</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2036,10 +2036,10 @@
         <v>44</v>
       </c>
       <c r="D90">
-        <v>53391</v>
+        <v>55472</v>
       </c>
       <c r="E90">
-        <v>16164</v>
+        <v>16615</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2053,10 +2053,10 @@
         <v>44</v>
       </c>
       <c r="D91">
-        <v>5819</v>
+        <v>5979</v>
       </c>
       <c r="E91">
-        <v>2846</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2087,7 +2087,7 @@
         <v>44</v>
       </c>
       <c r="D93">
-        <v>9936</v>
+        <v>9937</v>
       </c>
       <c r="E93">
         <v>4947</v>
@@ -2104,10 +2104,10 @@
         <v>44</v>
       </c>
       <c r="D94">
-        <v>35124</v>
+        <v>36436</v>
       </c>
       <c r="E94">
-        <v>14117</v>
+        <v>14575</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2138,10 +2138,10 @@
         <v>44</v>
       </c>
       <c r="D96">
-        <v>167876</v>
+        <v>176497</v>
       </c>
       <c r="E96">
-        <v>63586</v>
+        <v>65722</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2155,10 +2155,10 @@
         <v>44</v>
       </c>
       <c r="D97">
-        <v>3290</v>
+        <v>3356</v>
       </c>
       <c r="E97">
-        <v>1597</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2172,10 +2172,10 @@
         <v>44</v>
       </c>
       <c r="D98">
-        <v>13251</v>
+        <v>13485</v>
       </c>
       <c r="E98">
-        <v>6411</v>
+        <v>6479</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2189,10 +2189,10 @@
         <v>44</v>
       </c>
       <c r="D99">
-        <v>119588</v>
+        <v>124753</v>
       </c>
       <c r="E99">
-        <v>46874</v>
+        <v>48183</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2206,10 +2206,10 @@
         <v>44</v>
       </c>
       <c r="D100">
-        <v>203692</v>
+        <v>219088</v>
       </c>
       <c r="E100">
-        <v>79946</v>
+        <v>84103</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2223,10 +2223,10 @@
         <v>44</v>
       </c>
       <c r="D101">
-        <v>155358</v>
+        <v>160500</v>
       </c>
       <c r="E101">
-        <v>65915</v>
+        <v>67484</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2240,10 +2240,10 @@
         <v>44</v>
       </c>
       <c r="D102">
-        <v>236671</v>
+        <v>245929</v>
       </c>
       <c r="E102">
-        <v>87473</v>
+        <v>89875</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2257,10 +2257,10 @@
         <v>44</v>
       </c>
       <c r="D103">
-        <v>199605</v>
+        <v>208898</v>
       </c>
       <c r="E103">
-        <v>89663</v>
+        <v>92398</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2274,10 +2274,10 @@
         <v>44</v>
       </c>
       <c r="D104">
-        <v>42626</v>
+        <v>45908</v>
       </c>
       <c r="E104">
-        <v>20084</v>
+        <v>21175</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2291,10 +2291,10 @@
         <v>44</v>
       </c>
       <c r="D105">
-        <v>23042</v>
+        <v>23526</v>
       </c>
       <c r="E105">
-        <v>9584</v>
+        <v>9716</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2308,10 +2308,10 @@
         <v>44</v>
       </c>
       <c r="D106">
-        <v>18325</v>
+        <v>18530</v>
       </c>
       <c r="E106">
-        <v>9281</v>
+        <v>9364</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2325,10 +2325,10 @@
         <v>44</v>
       </c>
       <c r="D107">
-        <v>289933</v>
+        <v>296559</v>
       </c>
       <c r="E107">
-        <v>115221</v>
+        <v>116974</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2359,10 +2359,10 @@
         <v>44</v>
       </c>
       <c r="D109">
-        <v>121857</v>
+        <v>126871</v>
       </c>
       <c r="E109">
-        <v>47621</v>
+        <v>48829</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2376,10 +2376,10 @@
         <v>44</v>
       </c>
       <c r="D110">
-        <v>156508</v>
+        <v>161293</v>
       </c>
       <c r="E110">
-        <v>65806</v>
+        <v>67279</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2393,10 +2393,10 @@
         <v>44</v>
       </c>
       <c r="D111">
-        <v>303308</v>
+        <v>303313</v>
       </c>
       <c r="E111">
-        <v>111983</v>
+        <v>111984</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2410,10 +2410,10 @@
         <v>44</v>
       </c>
       <c r="D112">
-        <v>176202</v>
+        <v>176238</v>
       </c>
       <c r="E112">
-        <v>71084</v>
+        <v>71103</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2427,10 +2427,10 @@
         <v>44</v>
       </c>
       <c r="D113">
-        <v>38345</v>
+        <v>39232</v>
       </c>
       <c r="E113">
-        <v>11121</v>
+        <v>11242</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2444,10 +2444,10 @@
         <v>44</v>
       </c>
       <c r="D114">
-        <v>186636</v>
+        <v>194149</v>
       </c>
       <c r="E114">
-        <v>70056</v>
+        <v>71930</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2461,10 +2461,10 @@
         <v>44</v>
       </c>
       <c r="D115">
-        <v>12616</v>
+        <v>12772</v>
       </c>
       <c r="E115">
-        <v>6585</v>
+        <v>6635</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2478,10 +2478,10 @@
         <v>44</v>
       </c>
       <c r="D116">
-        <v>2509</v>
+        <v>2646</v>
       </c>
       <c r="E116">
-        <v>935</v>
+        <v>999</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2495,10 +2495,10 @@
         <v>44</v>
       </c>
       <c r="D117">
-        <v>4827</v>
+        <v>4857</v>
       </c>
       <c r="E117">
-        <v>2095</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2512,10 +2512,10 @@
         <v>44</v>
       </c>
       <c r="D118">
-        <v>292773</v>
+        <v>296288</v>
       </c>
       <c r="E118">
-        <v>82126</v>
+        <v>82446</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2529,10 +2529,10 @@
         <v>45</v>
       </c>
       <c r="D119">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="E119">
-        <v>308</v>
+        <v>317</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2546,10 +2546,10 @@
         <v>45</v>
       </c>
       <c r="D120">
-        <v>26128</v>
+        <v>26978</v>
       </c>
       <c r="E120">
-        <v>15747</v>
+        <v>16215</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2563,10 +2563,10 @@
         <v>45</v>
       </c>
       <c r="D121">
-        <v>1434</v>
+        <v>1496</v>
       </c>
       <c r="E121">
-        <v>945</v>
+        <v>986</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2580,10 +2580,10 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>1331</v>
+        <v>1352</v>
       </c>
       <c r="E122">
-        <v>931</v>
+        <v>946</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2614,10 +2614,10 @@
         <v>45</v>
       </c>
       <c r="D124">
-        <v>2746</v>
+        <v>2888</v>
       </c>
       <c r="E124">
-        <v>1796</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2665,10 +2665,10 @@
         <v>45</v>
       </c>
       <c r="D127">
-        <v>4537</v>
+        <v>4841</v>
       </c>
       <c r="E127">
-        <v>3095</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2682,10 +2682,10 @@
         <v>45</v>
       </c>
       <c r="D128">
-        <v>9037</v>
+        <v>9491</v>
       </c>
       <c r="E128">
-        <v>5827</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -2699,10 +2699,10 @@
         <v>45</v>
       </c>
       <c r="D129">
-        <v>693</v>
+        <v>729</v>
       </c>
       <c r="E129">
-        <v>541</v>
+        <v>567</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -2716,10 +2716,10 @@
         <v>45</v>
       </c>
       <c r="D130">
-        <v>4088</v>
+        <v>4303</v>
       </c>
       <c r="E130">
-        <v>2975</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2750,10 +2750,10 @@
         <v>45</v>
       </c>
       <c r="D132">
-        <v>2725</v>
+        <v>2797</v>
       </c>
       <c r="E132">
-        <v>1583</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2784,10 +2784,10 @@
         <v>45</v>
       </c>
       <c r="D134">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="E134">
-        <v>297</v>
+        <v>307</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2818,10 +2818,10 @@
         <v>45</v>
       </c>
       <c r="D136">
-        <v>8567</v>
+        <v>8960</v>
       </c>
       <c r="E136">
-        <v>5554</v>
+        <v>5829</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2835,10 +2835,10 @@
         <v>45</v>
       </c>
       <c r="D137">
-        <v>869</v>
+        <v>911</v>
       </c>
       <c r="E137">
-        <v>754</v>
+        <v>791</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2852,10 +2852,10 @@
         <v>45</v>
       </c>
       <c r="D138">
-        <v>5812</v>
+        <v>5989</v>
       </c>
       <c r="E138">
-        <v>4207</v>
+        <v>4339</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2869,10 +2869,10 @@
         <v>45</v>
       </c>
       <c r="D139">
-        <v>4871</v>
+        <v>5034</v>
       </c>
       <c r="E139">
-        <v>3370</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2886,10 +2886,10 @@
         <v>45</v>
       </c>
       <c r="D140">
-        <v>3152</v>
+        <v>3619</v>
       </c>
       <c r="E140">
-        <v>2139</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -2903,10 +2903,10 @@
         <v>45</v>
       </c>
       <c r="D141">
-        <v>6375</v>
+        <v>6473</v>
       </c>
       <c r="E141">
-        <v>5187</v>
+        <v>5263</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2920,10 +2920,10 @@
         <v>45</v>
       </c>
       <c r="D142">
-        <v>930</v>
+        <v>961</v>
       </c>
       <c r="E142">
-        <v>755</v>
+        <v>778</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -2954,10 +2954,10 @@
         <v>45</v>
       </c>
       <c r="D144">
-        <v>2071</v>
+        <v>2145</v>
       </c>
       <c r="E144">
-        <v>1520</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -2971,10 +2971,10 @@
         <v>45</v>
       </c>
       <c r="D145">
-        <v>1340</v>
+        <v>1374</v>
       </c>
       <c r="E145">
-        <v>1132</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -2988,10 +2988,10 @@
         <v>45</v>
       </c>
       <c r="D146">
-        <v>2540</v>
+        <v>2648</v>
       </c>
       <c r="E146">
-        <v>1994</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3005,10 +3005,10 @@
         <v>41</v>
       </c>
       <c r="D147">
-        <v>245534</v>
+        <v>254762</v>
       </c>
       <c r="E147">
-        <v>93589</v>
+        <v>95660</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3022,10 +3022,10 @@
         <v>41</v>
       </c>
       <c r="D148">
-        <v>994292</v>
+        <v>1035573</v>
       </c>
       <c r="E148">
-        <v>365521</v>
+        <v>375320</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3039,10 +3039,10 @@
         <v>41</v>
       </c>
       <c r="D149">
-        <v>61476</v>
+        <v>65044</v>
       </c>
       <c r="E149">
-        <v>21310</v>
+        <v>22136</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3056,10 +3056,10 @@
         <v>41</v>
       </c>
       <c r="D150">
-        <v>7461</v>
+        <v>7513</v>
       </c>
       <c r="E150">
-        <v>3140</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3073,10 +3073,10 @@
         <v>41</v>
       </c>
       <c r="D151">
-        <v>15986</v>
+        <v>16339</v>
       </c>
       <c r="E151">
-        <v>6509</v>
+        <v>6588</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3090,10 +3090,10 @@
         <v>41</v>
       </c>
       <c r="D152">
-        <v>15134</v>
+        <v>15335</v>
       </c>
       <c r="E152">
-        <v>6562</v>
+        <v>6611</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3107,10 +3107,10 @@
         <v>41</v>
       </c>
       <c r="D153">
-        <v>68146</v>
+        <v>71117</v>
       </c>
       <c r="E153">
-        <v>23572</v>
+        <v>24228</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3124,10 +3124,10 @@
         <v>41</v>
       </c>
       <c r="D154">
-        <v>56296</v>
+        <v>56792</v>
       </c>
       <c r="E154">
-        <v>24320</v>
+        <v>24452</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3141,10 +3141,10 @@
         <v>41</v>
       </c>
       <c r="D155">
-        <v>241374</v>
+        <v>253906</v>
       </c>
       <c r="E155">
-        <v>83727</v>
+        <v>86439</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3158,10 +3158,10 @@
         <v>41</v>
       </c>
       <c r="D156">
-        <v>4535</v>
+        <v>4647</v>
       </c>
       <c r="E156">
-        <v>1976</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3175,10 +3175,10 @@
         <v>41</v>
       </c>
       <c r="D157">
-        <v>13563</v>
+        <v>13954</v>
       </c>
       <c r="E157">
-        <v>6720</v>
+        <v>6866</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3192,10 +3192,10 @@
         <v>41</v>
       </c>
       <c r="D158">
-        <v>146278</v>
+        <v>151510</v>
       </c>
       <c r="E158">
-        <v>54470</v>
+        <v>55621</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3209,10 +3209,10 @@
         <v>41</v>
       </c>
       <c r="D159">
-        <v>307075</v>
+        <v>308938</v>
       </c>
       <c r="E159">
-        <v>84911</v>
+        <v>85425</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3226,10 +3226,10 @@
         <v>41</v>
       </c>
       <c r="D160">
-        <v>239523</v>
+        <v>248347</v>
       </c>
       <c r="E160">
-        <v>89237</v>
+        <v>91143</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3243,10 +3243,10 @@
         <v>41</v>
       </c>
       <c r="D161">
-        <v>346667</v>
+        <v>361983</v>
       </c>
       <c r="E161">
-        <v>118404</v>
+        <v>121604</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3260,10 +3260,10 @@
         <v>41</v>
       </c>
       <c r="D162">
-        <v>5814</v>
+        <v>6084</v>
       </c>
       <c r="E162">
-        <v>2705</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3277,10 +3277,10 @@
         <v>41</v>
       </c>
       <c r="D163">
-        <v>257212</v>
+        <v>265407</v>
       </c>
       <c r="E163">
-        <v>106677</v>
+        <v>108636</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3294,10 +3294,10 @@
         <v>41</v>
       </c>
       <c r="D164">
-        <v>50850</v>
+        <v>51057</v>
       </c>
       <c r="E164">
-        <v>23231</v>
+        <v>23297</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3311,10 +3311,10 @@
         <v>41</v>
       </c>
       <c r="D165">
-        <v>26241</v>
+        <v>27240</v>
       </c>
       <c r="E165">
-        <v>9548</v>
+        <v>9758</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3328,10 +3328,10 @@
         <v>41</v>
       </c>
       <c r="D166">
-        <v>22736</v>
+        <v>23418</v>
       </c>
       <c r="E166">
-        <v>10298</v>
+        <v>10504</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3345,10 +3345,10 @@
         <v>41</v>
       </c>
       <c r="D167">
-        <v>463750</v>
+        <v>472751</v>
       </c>
       <c r="E167">
-        <v>161564</v>
+        <v>163689</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3379,10 +3379,10 @@
         <v>41</v>
       </c>
       <c r="D169">
-        <v>170565</v>
+        <v>177455</v>
       </c>
       <c r="E169">
-        <v>59848</v>
+        <v>61394</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3396,10 +3396,10 @@
         <v>41</v>
       </c>
       <c r="D170">
-        <v>205259</v>
+        <v>212871</v>
       </c>
       <c r="E170">
-        <v>79738</v>
+        <v>81705</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3413,10 +3413,10 @@
         <v>41</v>
       </c>
       <c r="D171">
-        <v>385517</v>
+        <v>394350</v>
       </c>
       <c r="E171">
-        <v>148353</v>
+        <v>150723</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3430,7 +3430,7 @@
         <v>41</v>
       </c>
       <c r="D172">
-        <v>230715</v>
+        <v>230718</v>
       </c>
       <c r="E172">
         <v>76080</v>
@@ -3447,10 +3447,10 @@
         <v>41</v>
       </c>
       <c r="D173">
-        <v>139041</v>
+        <v>143846</v>
       </c>
       <c r="E173">
-        <v>39749</v>
+        <v>40858</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3464,10 +3464,10 @@
         <v>41</v>
       </c>
       <c r="D174">
-        <v>229148</v>
+        <v>238695</v>
       </c>
       <c r="E174">
-        <v>86271</v>
+        <v>88364</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3481,10 +3481,10 @@
         <v>41</v>
       </c>
       <c r="D175">
-        <v>17738</v>
+        <v>18402</v>
       </c>
       <c r="E175">
-        <v>8630</v>
+        <v>8864</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3498,10 +3498,10 @@
         <v>41</v>
       </c>
       <c r="D176">
-        <v>22775</v>
+        <v>24183</v>
       </c>
       <c r="E176">
-        <v>9217</v>
+        <v>9608</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3515,10 +3515,10 @@
         <v>41</v>
       </c>
       <c r="D177">
-        <v>67593</v>
+        <v>71325</v>
       </c>
       <c r="E177">
-        <v>30224</v>
+        <v>31313</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3532,10 +3532,10 @@
         <v>41</v>
       </c>
       <c r="D178">
-        <v>361666</v>
+        <v>382672</v>
       </c>
       <c r="E178">
-        <v>98116</v>
+        <v>101966</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3549,10 +3549,10 @@
         <v>42</v>
       </c>
       <c r="D179">
-        <v>1738</v>
+        <v>1795</v>
       </c>
       <c r="E179">
-        <v>1524</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3566,10 +3566,10 @@
         <v>42</v>
       </c>
       <c r="D180">
-        <v>35386</v>
+        <v>36697</v>
       </c>
       <c r="E180">
-        <v>25607</v>
+        <v>26487</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3583,10 +3583,10 @@
         <v>42</v>
       </c>
       <c r="D181">
-        <v>1486</v>
+        <v>1550</v>
       </c>
       <c r="E181">
-        <v>1083</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3600,10 +3600,10 @@
         <v>42</v>
       </c>
       <c r="D182">
-        <v>1336</v>
+        <v>1399</v>
       </c>
       <c r="E182">
-        <v>1119</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3617,10 +3617,10 @@
         <v>42</v>
       </c>
       <c r="D183">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="E183">
-        <v>225</v>
+        <v>245</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3634,10 +3634,10 @@
         <v>42</v>
       </c>
       <c r="D184">
-        <v>3447</v>
+        <v>3583</v>
       </c>
       <c r="E184">
-        <v>3034</v>
+        <v>3162</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3685,10 +3685,10 @@
         <v>42</v>
       </c>
       <c r="D187">
-        <v>5905</v>
+        <v>6143</v>
       </c>
       <c r="E187">
-        <v>4835</v>
+        <v>5031</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3702,10 +3702,10 @@
         <v>42</v>
       </c>
       <c r="D188">
-        <v>12166</v>
+        <v>12833</v>
       </c>
       <c r="E188">
-        <v>8499</v>
+        <v>8973</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -3719,10 +3719,10 @@
         <v>42</v>
       </c>
       <c r="D189">
-        <v>2810</v>
+        <v>2855</v>
       </c>
       <c r="E189">
-        <v>2213</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3736,10 +3736,10 @@
         <v>42</v>
       </c>
       <c r="D190">
-        <v>7359</v>
+        <v>7635</v>
       </c>
       <c r="E190">
-        <v>6049</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3770,10 +3770,10 @@
         <v>42</v>
       </c>
       <c r="D192">
-        <v>2633</v>
+        <v>2789</v>
       </c>
       <c r="E192">
-        <v>2315</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3838,10 +3838,10 @@
         <v>42</v>
       </c>
       <c r="D196">
-        <v>19594</v>
+        <v>20436</v>
       </c>
       <c r="E196">
-        <v>10065</v>
+        <v>10561</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3855,10 +3855,10 @@
         <v>42</v>
       </c>
       <c r="D197">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E197">
-        <v>66</v>
+        <v>83</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3872,10 +3872,10 @@
         <v>42</v>
       </c>
       <c r="D198">
-        <v>2077</v>
+        <v>2112</v>
       </c>
       <c r="E198">
-        <v>1865</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3889,10 +3889,10 @@
         <v>42</v>
       </c>
       <c r="D199">
-        <v>11244</v>
+        <v>11685</v>
       </c>
       <c r="E199">
-        <v>7927</v>
+        <v>8198</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3906,10 +3906,10 @@
         <v>42</v>
       </c>
       <c r="D200">
-        <v>7997</v>
+        <v>8250</v>
       </c>
       <c r="E200">
-        <v>6551</v>
+        <v>6762</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3923,10 +3923,10 @@
         <v>42</v>
       </c>
       <c r="D201">
-        <v>5275</v>
+        <v>6248</v>
       </c>
       <c r="E201">
-        <v>4470</v>
+        <v>5302</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3940,10 +3940,10 @@
         <v>42</v>
       </c>
       <c r="D202">
-        <v>27701</v>
+        <v>27913</v>
       </c>
       <c r="E202">
-        <v>8418</v>
+        <v>8561</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -3957,10 +3957,10 @@
         <v>42</v>
       </c>
       <c r="D203">
-        <v>2479</v>
+        <v>2591</v>
       </c>
       <c r="E203">
-        <v>2116</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3974,10 +3974,10 @@
         <v>42</v>
       </c>
       <c r="D204">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="E204">
-        <v>559</v>
+        <v>565</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -3991,10 +3991,10 @@
         <v>42</v>
       </c>
       <c r="D205">
-        <v>4567</v>
+        <v>4759</v>
       </c>
       <c r="E205">
-        <v>3250</v>
+        <v>3398</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -4008,10 +4008,10 @@
         <v>42</v>
       </c>
       <c r="D206">
-        <v>2724</v>
+        <v>2792</v>
       </c>
       <c r="E206">
-        <v>2188</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -4025,10 +4025,10 @@
         <v>42</v>
       </c>
       <c r="D207">
-        <v>5315</v>
+        <v>5629</v>
       </c>
       <c r="E207">
-        <v>3947</v>
+        <v>4174</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -4042,10 +4042,10 @@
         <v>43</v>
       </c>
       <c r="D208">
-        <v>16487</v>
+        <v>16941</v>
       </c>
       <c r="E208">
-        <v>7048</v>
+        <v>7212</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -4059,10 +4059,10 @@
         <v>43</v>
       </c>
       <c r="D209">
-        <v>104545</v>
+        <v>109304</v>
       </c>
       <c r="E209">
-        <v>46939</v>
+        <v>48387</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -4076,10 +4076,10 @@
         <v>43</v>
       </c>
       <c r="D210">
-        <v>1954</v>
+        <v>2014</v>
       </c>
       <c r="E210">
-        <v>950</v>
+        <v>974</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -4110,10 +4110,10 @@
         <v>43</v>
       </c>
       <c r="D212">
-        <v>2970</v>
+        <v>3161</v>
       </c>
       <c r="E212">
-        <v>1476</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4127,10 +4127,10 @@
         <v>43</v>
       </c>
       <c r="D213">
-        <v>1169</v>
+        <v>1233</v>
       </c>
       <c r="E213">
-        <v>382</v>
+        <v>396</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4144,10 +4144,10 @@
         <v>43</v>
       </c>
       <c r="D214">
-        <v>15092</v>
+        <v>16229</v>
       </c>
       <c r="E214">
-        <v>6311</v>
+        <v>6801</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4178,10 +4178,10 @@
         <v>43</v>
       </c>
       <c r="D216">
-        <v>13922</v>
+        <v>14623</v>
       </c>
       <c r="E216">
-        <v>6554</v>
+        <v>6771</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4195,10 +4195,10 @@
         <v>43</v>
       </c>
       <c r="D217">
-        <v>26046</v>
+        <v>26575</v>
       </c>
       <c r="E217">
-        <v>8740</v>
+        <v>8947</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4212,10 +4212,10 @@
         <v>43</v>
       </c>
       <c r="D218">
-        <v>9043</v>
+        <v>9408</v>
       </c>
       <c r="E218">
-        <v>3786</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4229,10 +4229,10 @@
         <v>43</v>
       </c>
       <c r="D219">
-        <v>14863</v>
+        <v>15339</v>
       </c>
       <c r="E219">
-        <v>7555</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4246,10 +4246,10 @@
         <v>43</v>
       </c>
       <c r="D220">
-        <v>2382</v>
+        <v>2513</v>
       </c>
       <c r="E220">
-        <v>1316</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4263,10 +4263,10 @@
         <v>43</v>
       </c>
       <c r="D221">
-        <v>8830</v>
+        <v>9198</v>
       </c>
       <c r="E221">
-        <v>4649</v>
+        <v>4774</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4297,10 +4297,10 @@
         <v>43</v>
       </c>
       <c r="D223">
-        <v>1518</v>
+        <v>1595</v>
       </c>
       <c r="E223">
-        <v>872</v>
+        <v>898</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4314,10 +4314,10 @@
         <v>43</v>
       </c>
       <c r="D224">
-        <v>1436</v>
+        <v>1492</v>
       </c>
       <c r="E224">
-        <v>788</v>
+        <v>815</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4331,10 +4331,10 @@
         <v>43</v>
       </c>
       <c r="D225">
-        <v>67193</v>
+        <v>67594</v>
       </c>
       <c r="E225">
-        <v>24490</v>
+        <v>24598</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4365,10 +4365,10 @@
         <v>43</v>
       </c>
       <c r="D227">
-        <v>7881</v>
+        <v>8237</v>
       </c>
       <c r="E227">
-        <v>3585</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4382,10 +4382,10 @@
         <v>43</v>
       </c>
       <c r="D228">
-        <v>41381</v>
+        <v>42842</v>
       </c>
       <c r="E228">
-        <v>20938</v>
+        <v>21367</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4399,10 +4399,10 @@
         <v>43</v>
       </c>
       <c r="D229">
-        <v>29131</v>
+        <v>29403</v>
       </c>
       <c r="E229">
-        <v>12849</v>
+        <v>12934</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4433,10 +4433,10 @@
         <v>43</v>
       </c>
       <c r="D231">
-        <v>75338</v>
+        <v>76645</v>
       </c>
       <c r="E231">
-        <v>25454</v>
+        <v>25645</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4450,10 +4450,10 @@
         <v>43</v>
       </c>
       <c r="D232">
-        <v>9277</v>
+        <v>9580</v>
       </c>
       <c r="E232">
-        <v>4803</v>
+        <v>4906</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4467,10 +4467,10 @@
         <v>43</v>
       </c>
       <c r="D233">
-        <v>6642</v>
+        <v>6851</v>
       </c>
       <c r="E233">
-        <v>3238</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4484,10 +4484,10 @@
         <v>43</v>
       </c>
       <c r="D234">
-        <v>6358</v>
+        <v>6971</v>
       </c>
       <c r="E234">
-        <v>3346</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4501,10 +4501,10 @@
         <v>43</v>
       </c>
       <c r="D235">
-        <v>8618</v>
+        <v>9102</v>
       </c>
       <c r="E235">
-        <v>4355</v>
+        <v>4537</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4518,10 +4518,10 @@
         <v>43</v>
       </c>
       <c r="D236">
-        <v>18886</v>
+        <v>20156</v>
       </c>
       <c r="E236">
-        <v>7409</v>
+        <v>7709</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4535,10 +4535,10 @@
         <v>44</v>
       </c>
       <c r="D237">
-        <v>229047</v>
+        <v>237821</v>
       </c>
       <c r="E237">
-        <v>89957</v>
+        <v>91961</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4552,10 +4552,10 @@
         <v>44</v>
       </c>
       <c r="D238">
-        <v>889747</v>
+        <v>926269</v>
       </c>
       <c r="E238">
-        <v>346016</v>
+        <v>355424</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4569,10 +4569,10 @@
         <v>44</v>
       </c>
       <c r="D239">
-        <v>59522</v>
+        <v>63030</v>
       </c>
       <c r="E239">
-        <v>20651</v>
+        <v>21466</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4586,10 +4586,10 @@
         <v>44</v>
       </c>
       <c r="D240">
-        <v>7461</v>
+        <v>7513</v>
       </c>
       <c r="E240">
-        <v>3140</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4603,10 +4603,10 @@
         <v>44</v>
       </c>
       <c r="D241">
-        <v>15986</v>
+        <v>16339</v>
       </c>
       <c r="E241">
-        <v>6509</v>
+        <v>6588</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4620,10 +4620,10 @@
         <v>44</v>
       </c>
       <c r="D242">
-        <v>15133</v>
+        <v>15334</v>
       </c>
       <c r="E242">
-        <v>6561</v>
+        <v>6610</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4637,10 +4637,10 @@
         <v>44</v>
       </c>
       <c r="D243">
-        <v>65176</v>
+        <v>67956</v>
       </c>
       <c r="E243">
-        <v>22992</v>
+        <v>23624</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4654,10 +4654,10 @@
         <v>44</v>
       </c>
       <c r="D244">
-        <v>55127</v>
+        <v>55559</v>
       </c>
       <c r="E244">
-        <v>24146</v>
+        <v>24271</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4671,10 +4671,10 @@
         <v>44</v>
       </c>
       <c r="D245">
-        <v>226282</v>
+        <v>237677</v>
       </c>
       <c r="E245">
-        <v>81092</v>
+        <v>83626</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -4688,10 +4688,10 @@
         <v>44</v>
       </c>
       <c r="D246">
-        <v>4535</v>
+        <v>4647</v>
       </c>
       <c r="E246">
-        <v>1976</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -4705,10 +4705,10 @@
         <v>44</v>
       </c>
       <c r="D247">
-        <v>13562</v>
+        <v>13953</v>
       </c>
       <c r="E247">
-        <v>6719</v>
+        <v>6865</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -4722,10 +4722,10 @@
         <v>44</v>
       </c>
       <c r="D248">
-        <v>132356</v>
+        <v>136887</v>
       </c>
       <c r="E248">
-        <v>50834</v>
+        <v>51875</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -4739,10 +4739,10 @@
         <v>44</v>
       </c>
       <c r="D249">
-        <v>281029</v>
+        <v>282363</v>
       </c>
       <c r="E249">
-        <v>80322</v>
+        <v>80684</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4756,10 +4756,10 @@
         <v>44</v>
       </c>
       <c r="D250">
-        <v>230480</v>
+        <v>238939</v>
       </c>
       <c r="E250">
-        <v>87733</v>
+        <v>89611</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4773,10 +4773,10 @@
         <v>44</v>
       </c>
       <c r="D251">
-        <v>331804</v>
+        <v>346644</v>
       </c>
       <c r="E251">
-        <v>115442</v>
+        <v>118597</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4790,10 +4790,10 @@
         <v>44</v>
       </c>
       <c r="D252">
-        <v>3432</v>
+        <v>3571</v>
       </c>
       <c r="E252">
-        <v>1662</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4807,10 +4807,10 @@
         <v>44</v>
       </c>
       <c r="D253">
-        <v>248382</v>
+        <v>256209</v>
       </c>
       <c r="E253">
-        <v>104908</v>
+        <v>106838</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4824,10 +4824,10 @@
         <v>44</v>
       </c>
       <c r="D254">
-        <v>50819</v>
+        <v>51026</v>
       </c>
       <c r="E254">
-        <v>23223</v>
+        <v>23289</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4841,10 +4841,10 @@
         <v>44</v>
       </c>
       <c r="D255">
-        <v>24723</v>
+        <v>25645</v>
       </c>
       <c r="E255">
-        <v>9320</v>
+        <v>9523</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4858,10 +4858,10 @@
         <v>44</v>
       </c>
       <c r="D256">
-        <v>21300</v>
+        <v>21926</v>
       </c>
       <c r="E256">
-        <v>9872</v>
+        <v>10068</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4875,10 +4875,10 @@
         <v>44</v>
       </c>
       <c r="D257">
-        <v>396557</v>
+        <v>405157</v>
       </c>
       <c r="E257">
-        <v>151439</v>
+        <v>153572</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4909,10 +4909,10 @@
         <v>44</v>
       </c>
       <c r="D259">
-        <v>162684</v>
+        <v>169218</v>
       </c>
       <c r="E259">
-        <v>58642</v>
+        <v>60151</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4926,10 +4926,10 @@
         <v>44</v>
       </c>
       <c r="D260">
-        <v>163878</v>
+        <v>170029</v>
       </c>
       <c r="E260">
-        <v>67832</v>
+        <v>69649</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4943,10 +4943,10 @@
         <v>44</v>
       </c>
       <c r="D261">
-        <v>356386</v>
+        <v>364947</v>
       </c>
       <c r="E261">
-        <v>142590</v>
+        <v>144965</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4960,7 +4960,7 @@
         <v>44</v>
       </c>
       <c r="D262">
-        <v>199775</v>
+        <v>199778</v>
       </c>
       <c r="E262">
         <v>69996</v>
@@ -4977,10 +4977,10 @@
         <v>44</v>
       </c>
       <c r="D263">
-        <v>63703</v>
+        <v>67201</v>
       </c>
       <c r="E263">
-        <v>21252</v>
+        <v>22414</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -4994,10 +4994,10 @@
         <v>44</v>
       </c>
       <c r="D264">
-        <v>219871</v>
+        <v>229115</v>
       </c>
       <c r="E264">
-        <v>84033</v>
+        <v>86091</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -5011,10 +5011,10 @@
         <v>44</v>
       </c>
       <c r="D265">
-        <v>11096</v>
+        <v>11551</v>
       </c>
       <c r="E265">
-        <v>6069</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -5028,10 +5028,10 @@
         <v>44</v>
       </c>
       <c r="D266">
-        <v>16417</v>
+        <v>17212</v>
       </c>
       <c r="E266">
-        <v>7516</v>
+        <v>7793</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -5045,10 +5045,10 @@
         <v>44</v>
       </c>
       <c r="D267">
-        <v>58975</v>
+        <v>62223</v>
       </c>
       <c r="E267">
-        <v>27553</v>
+        <v>28581</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -5062,10 +5062,10 @@
         <v>44</v>
       </c>
       <c r="D268">
-        <v>342780</v>
+        <v>362516</v>
       </c>
       <c r="E268">
-        <v>94733</v>
+        <v>98489</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -5079,10 +5079,10 @@
         <v>45</v>
       </c>
       <c r="D269">
-        <v>601</v>
+        <v>623</v>
       </c>
       <c r="E269">
-        <v>514</v>
+        <v>534</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -5096,10 +5096,10 @@
         <v>45</v>
       </c>
       <c r="D270">
-        <v>24742</v>
+        <v>25786</v>
       </c>
       <c r="E270">
-        <v>14824</v>
+        <v>15394</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -5113,10 +5113,10 @@
         <v>45</v>
       </c>
       <c r="D271">
-        <v>1421</v>
+        <v>1502</v>
       </c>
       <c r="E271">
-        <v>746</v>
+        <v>789</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -5130,10 +5130,10 @@
         <v>45</v>
       </c>
       <c r="D272">
-        <v>722</v>
+        <v>745</v>
       </c>
       <c r="E272">
-        <v>566</v>
+        <v>584</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -5147,10 +5147,10 @@
         <v>45</v>
       </c>
       <c r="D273">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E273">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5164,10 +5164,10 @@
         <v>45</v>
       </c>
       <c r="D274">
-        <v>2842</v>
+        <v>2955</v>
       </c>
       <c r="E274">
-        <v>1964</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5215,10 +5215,10 @@
         <v>45</v>
       </c>
       <c r="D277">
-        <v>4229</v>
+        <v>4422</v>
       </c>
       <c r="E277">
-        <v>2916</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5232,10 +5232,10 @@
         <v>45</v>
       </c>
       <c r="D278">
-        <v>7975</v>
+        <v>8509</v>
       </c>
       <c r="E278">
-        <v>5314</v>
+        <v>5642</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5249,10 +5249,10 @@
         <v>45</v>
       </c>
       <c r="D279">
-        <v>1560</v>
+        <v>1567</v>
       </c>
       <c r="E279">
-        <v>1070</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5266,10 +5266,10 @@
         <v>45</v>
       </c>
       <c r="D280">
-        <v>3106</v>
+        <v>3269</v>
       </c>
       <c r="E280">
-        <v>2441</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5300,10 +5300,10 @@
         <v>45</v>
       </c>
       <c r="D282">
-        <v>1850</v>
+        <v>1938</v>
       </c>
       <c r="E282">
-        <v>1266</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5368,10 +5368,10 @@
         <v>45</v>
       </c>
       <c r="D286">
-        <v>8610</v>
+        <v>9104</v>
       </c>
       <c r="E286">
-        <v>6147</v>
+        <v>6490</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5385,10 +5385,10 @@
         <v>45</v>
       </c>
       <c r="D287">
-        <v>1590</v>
+        <v>1633</v>
       </c>
       <c r="E287">
-        <v>1293</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -5402,10 +5402,10 @@
         <v>45</v>
       </c>
       <c r="D288">
-        <v>6591</v>
+        <v>6942</v>
       </c>
       <c r="E288">
-        <v>4871</v>
+        <v>5092</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -5419,10 +5419,10 @@
         <v>45</v>
       </c>
       <c r="D289">
-        <v>4443</v>
+        <v>4633</v>
       </c>
       <c r="E289">
-        <v>3033</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5436,10 +5436,10 @@
         <v>45</v>
       </c>
       <c r="D290">
-        <v>3359</v>
+        <v>3987</v>
       </c>
       <c r="E290">
-        <v>2425</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5453,10 +5453,10 @@
         <v>45</v>
       </c>
       <c r="D291">
-        <v>6275</v>
+        <v>6377</v>
       </c>
       <c r="E291">
-        <v>5167</v>
+        <v>5246</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -5470,10 +5470,10 @@
         <v>45</v>
       </c>
       <c r="D292">
-        <v>1005</v>
+        <v>1052</v>
       </c>
       <c r="E292">
-        <v>779</v>
+        <v>813</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -5487,10 +5487,10 @@
         <v>45</v>
       </c>
       <c r="D293">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E293">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -5504,10 +5504,10 @@
         <v>45</v>
       </c>
       <c r="D294">
-        <v>2231</v>
+        <v>2329</v>
       </c>
       <c r="E294">
-        <v>1602</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5521,10 +5521,10 @@
         <v>45</v>
       </c>
       <c r="D295">
-        <v>1421</v>
+        <v>1463</v>
       </c>
       <c r="E295">
-        <v>1165</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5538,10 +5538,10 @@
         <v>45</v>
       </c>
       <c r="D296">
-        <v>3121</v>
+        <v>3296</v>
       </c>
       <c r="E296">
-        <v>2247</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -6099,10 +6099,10 @@
         <v>42</v>
       </c>
       <c r="D329">
-        <v>2707</v>
+        <v>2777</v>
       </c>
       <c r="E329">
-        <v>2312</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -6116,10 +6116,10 @@
         <v>42</v>
       </c>
       <c r="D330">
-        <v>36601</v>
+        <v>38037</v>
       </c>
       <c r="E330">
-        <v>27473</v>
+        <v>28498</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -6133,10 +6133,10 @@
         <v>42</v>
       </c>
       <c r="D331">
-        <v>1716</v>
+        <v>1813</v>
       </c>
       <c r="E331">
-        <v>1262</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -6167,10 +6167,10 @@
         <v>42</v>
       </c>
       <c r="D333">
-        <v>1757</v>
+        <v>1774</v>
       </c>
       <c r="E333">
-        <v>1290</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6184,10 +6184,10 @@
         <v>42</v>
       </c>
       <c r="D334">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="E334">
-        <v>416</v>
+        <v>427</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -6201,10 +6201,10 @@
         <v>42</v>
       </c>
       <c r="D335">
-        <v>6227</v>
+        <v>6308</v>
       </c>
       <c r="E335">
-        <v>5398</v>
+        <v>5472</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -6218,10 +6218,10 @@
         <v>42</v>
       </c>
       <c r="D336">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E336">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6235,10 +6235,10 @@
         <v>42</v>
       </c>
       <c r="D337">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E337">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6252,10 +6252,10 @@
         <v>42</v>
       </c>
       <c r="D338">
-        <v>6047</v>
+        <v>6261</v>
       </c>
       <c r="E338">
-        <v>4951</v>
+        <v>5126</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6269,10 +6269,10 @@
         <v>42</v>
       </c>
       <c r="D339">
-        <v>10620</v>
+        <v>10987</v>
       </c>
       <c r="E339">
-        <v>7656</v>
+        <v>7907</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6286,10 +6286,10 @@
         <v>42</v>
       </c>
       <c r="D340">
-        <v>3613</v>
+        <v>3703</v>
       </c>
       <c r="E340">
-        <v>2786</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6303,10 +6303,10 @@
         <v>42</v>
       </c>
       <c r="D341">
-        <v>8783</v>
+        <v>9325</v>
       </c>
       <c r="E341">
-        <v>6994</v>
+        <v>7390</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -6337,10 +6337,10 @@
         <v>42</v>
       </c>
       <c r="D343">
-        <v>2448</v>
+        <v>2569</v>
       </c>
       <c r="E343">
-        <v>2011</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6354,10 +6354,10 @@
         <v>42</v>
       </c>
       <c r="D344">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E344">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6371,10 +6371,10 @@
         <v>42</v>
       </c>
       <c r="D345">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="E345">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6405,10 +6405,10 @@
         <v>42</v>
       </c>
       <c r="D347">
-        <v>23264</v>
+        <v>24123</v>
       </c>
       <c r="E347">
-        <v>11338</v>
+        <v>11751</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6439,10 +6439,10 @@
         <v>42</v>
       </c>
       <c r="D349">
-        <v>2024</v>
+        <v>2089</v>
       </c>
       <c r="E349">
-        <v>1821</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6456,10 +6456,10 @@
         <v>42</v>
       </c>
       <c r="D350">
-        <v>11261</v>
+        <v>11614</v>
       </c>
       <c r="E350">
-        <v>7742</v>
+        <v>7959</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6473,10 +6473,10 @@
         <v>42</v>
       </c>
       <c r="D351">
-        <v>8603</v>
+        <v>8936</v>
       </c>
       <c r="E351">
-        <v>7106</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6507,10 +6507,10 @@
         <v>42</v>
       </c>
       <c r="D353">
-        <v>26109</v>
+        <v>26260</v>
       </c>
       <c r="E353">
-        <v>7410</v>
+        <v>7525</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -6524,10 +6524,10 @@
         <v>42</v>
       </c>
       <c r="D354">
-        <v>2485</v>
+        <v>2562</v>
       </c>
       <c r="E354">
-        <v>2137</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6541,10 +6541,10 @@
         <v>42</v>
       </c>
       <c r="D355">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="E355">
-        <v>617</v>
+        <v>623</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6558,10 +6558,10 @@
         <v>42</v>
       </c>
       <c r="D356">
-        <v>4670</v>
+        <v>4888</v>
       </c>
       <c r="E356">
-        <v>3719</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6575,10 +6575,10 @@
         <v>42</v>
       </c>
       <c r="D357">
-        <v>2711</v>
+        <v>2804</v>
       </c>
       <c r="E357">
-        <v>2294</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6592,10 +6592,10 @@
         <v>42</v>
       </c>
       <c r="D358">
-        <v>4679</v>
+        <v>4897</v>
       </c>
       <c r="E358">
-        <v>3599</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -7629,10 +7629,10 @@
         <v>45</v>
       </c>
       <c r="D419">
-        <v>1120</v>
+        <v>1156</v>
       </c>
       <c r="E419">
-        <v>940</v>
+        <v>962</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -7646,10 +7646,10 @@
         <v>45</v>
       </c>
       <c r="D420">
-        <v>23581</v>
+        <v>24696</v>
       </c>
       <c r="E420">
-        <v>13989</v>
+        <v>14594</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -7663,10 +7663,10 @@
         <v>45</v>
       </c>
       <c r="D421">
-        <v>1284</v>
+        <v>1303</v>
       </c>
       <c r="E421">
-        <v>715</v>
+        <v>731</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7697,10 +7697,10 @@
         <v>45</v>
       </c>
       <c r="D423">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="E423">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -7714,10 +7714,10 @@
         <v>45</v>
       </c>
       <c r="D424">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E424">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -7731,10 +7731,10 @@
         <v>45</v>
       </c>
       <c r="D425">
-        <v>4562</v>
+        <v>4640</v>
       </c>
       <c r="E425">
-        <v>3162</v>
+        <v>3211</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -7765,10 +7765,10 @@
         <v>45</v>
       </c>
       <c r="D427">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E427">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -7782,10 +7782,10 @@
         <v>45</v>
       </c>
       <c r="D428">
-        <v>4221</v>
+        <v>4373</v>
       </c>
       <c r="E428">
-        <v>2935</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -7799,10 +7799,10 @@
         <v>45</v>
       </c>
       <c r="D429">
-        <v>7292</v>
+        <v>7528</v>
       </c>
       <c r="E429">
-        <v>4986</v>
+        <v>5158</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -7816,10 +7816,10 @@
         <v>45</v>
       </c>
       <c r="D430">
-        <v>2088</v>
+        <v>2154</v>
       </c>
       <c r="E430">
-        <v>1487</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -7833,10 +7833,10 @@
         <v>45</v>
       </c>
       <c r="D431">
-        <v>3028</v>
+        <v>3210</v>
       </c>
       <c r="E431">
-        <v>2316</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -7867,10 +7867,10 @@
         <v>45</v>
       </c>
       <c r="D433">
-        <v>1776</v>
+        <v>1868</v>
       </c>
       <c r="E433">
-        <v>1162</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -7884,10 +7884,10 @@
         <v>45</v>
       </c>
       <c r="D434">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E434">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -7901,10 +7901,10 @@
         <v>45</v>
       </c>
       <c r="D435">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="E435">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -7935,10 +7935,10 @@
         <v>45</v>
       </c>
       <c r="D437">
-        <v>11335</v>
+        <v>11859</v>
       </c>
       <c r="E437">
-        <v>7322</v>
+        <v>7637</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -7969,10 +7969,10 @@
         <v>45</v>
       </c>
       <c r="D439">
-        <v>1237</v>
+        <v>1264</v>
       </c>
       <c r="E439">
-        <v>1021</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -7986,10 +7986,10 @@
         <v>45</v>
       </c>
       <c r="D440">
-        <v>8054</v>
+        <v>8312</v>
       </c>
       <c r="E440">
-        <v>5641</v>
+        <v>5823</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -8003,10 +8003,10 @@
         <v>45</v>
       </c>
       <c r="D441">
-        <v>4586</v>
+        <v>4737</v>
       </c>
       <c r="E441">
-        <v>3163</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -8037,10 +8037,10 @@
         <v>45</v>
       </c>
       <c r="D443">
-        <v>5672</v>
+        <v>5759</v>
       </c>
       <c r="E443">
-        <v>4467</v>
+        <v>4537</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -8054,10 +8054,10 @@
         <v>45</v>
       </c>
       <c r="D444">
-        <v>1005</v>
+        <v>1034</v>
       </c>
       <c r="E444">
-        <v>810</v>
+        <v>831</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -8088,10 +8088,10 @@
         <v>45</v>
       </c>
       <c r="D446">
-        <v>2339</v>
+        <v>2460</v>
       </c>
       <c r="E446">
-        <v>1803</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -8105,10 +8105,10 @@
         <v>45</v>
       </c>
       <c r="D447">
-        <v>1461</v>
+        <v>1523</v>
       </c>
       <c r="E447">
-        <v>1219</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -8122,10 +8122,10 @@
         <v>45</v>
       </c>
       <c r="D448">
-        <v>2893</v>
+        <v>3039</v>
       </c>
       <c r="E448">
-        <v>2159</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="449" spans="2:5">
@@ -8296,237 +8296,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010086ADF0657346C74FA4159949F83B0105" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e679190041f368e5f1999762c1635bea">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ecbbb845-5bb4-49a6-a031-2c6210f1a021" xmlns:ns3="2311af43-dfdb-495f-8272-1d5374a07a4f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="106f98ec6a760573afb5fafd9fd455c8" ns2:_="" ns3:_="">
-    <xsd:import namespace="ecbbb845-5bb4-49a6-a031-2c6210f1a021"/>
-    <xsd:import namespace="2311af43-dfdb-495f-8272-1d5374a07a4f"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ecbbb845-5bb4-49a6-a031-2c6210f1a021" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6c7de3c9-8e68-46a6-abfc-7512e1ae618b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2311af43-dfdb-495f-8272-1d5374a07a4f" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{57b665d3-a353-4c8b-994f-ed147fe15c37}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="2311af43-dfdb-495f-8272-1d5374a07a4f">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ecbbb845-5bb4-49a6-a031-2c6210f1a021">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2311af43-dfdb-495f-8272-1d5374a07a4f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B151228D-BDFE-4FCC-8F9E-A80657B2667D}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04F87B6C-E3DC-4795-86AB-8E61058B7CB1}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37E88904-1744-4031-AA59-EC44D4DA3F72}"/>
 </file>
--- a/data/plan_justicia/procedimientos_personas_plan_justicia.xlsx
+++ b/data/plan_justicia/procedimientos_personas_plan_justicia.xlsx
@@ -5555,10 +5555,10 @@
         <v>41</v>
       </c>
       <c r="D297">
-        <v>318116</v>
+        <v>330191</v>
       </c>
       <c r="E297">
-        <v>111101</v>
+        <v>113375</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5572,10 +5572,10 @@
         <v>41</v>
       </c>
       <c r="D298">
-        <v>1026374</v>
+        <v>1068042</v>
       </c>
       <c r="E298">
-        <v>355247</v>
+        <v>366604</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5589,10 +5589,10 @@
         <v>41</v>
       </c>
       <c r="D299">
-        <v>86274</v>
+        <v>89977</v>
       </c>
       <c r="E299">
-        <v>27032</v>
+        <v>27682</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5606,10 +5606,10 @@
         <v>41</v>
       </c>
       <c r="D300">
-        <v>7344</v>
+        <v>8103</v>
       </c>
       <c r="E300">
-        <v>3750</v>
+        <v>3949</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5623,10 +5623,10 @@
         <v>41</v>
       </c>
       <c r="D301">
-        <v>14539</v>
+        <v>14871</v>
       </c>
       <c r="E301">
-        <v>6008</v>
+        <v>6095</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5640,10 +5640,10 @@
         <v>41</v>
       </c>
       <c r="D302">
-        <v>18569</v>
+        <v>19981</v>
       </c>
       <c r="E302">
-        <v>7874</v>
+        <v>8256</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -5657,10 +5657,10 @@
         <v>41</v>
       </c>
       <c r="D303">
-        <v>84362</v>
+        <v>87336</v>
       </c>
       <c r="E303">
-        <v>27345</v>
+        <v>27929</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5674,10 +5674,10 @@
         <v>41</v>
       </c>
       <c r="D304">
-        <v>56619</v>
+        <v>58411</v>
       </c>
       <c r="E304">
-        <v>24424</v>
+        <v>24923</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5691,10 +5691,10 @@
         <v>41</v>
       </c>
       <c r="D305">
-        <v>333824</v>
+        <v>347700</v>
       </c>
       <c r="E305">
-        <v>104835</v>
+        <v>107133</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5708,10 +5708,10 @@
         <v>41</v>
       </c>
       <c r="D306">
-        <v>4898</v>
+        <v>5110</v>
       </c>
       <c r="E306">
-        <v>2157</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5725,10 +5725,10 @@
         <v>41</v>
       </c>
       <c r="D307">
-        <v>16550</v>
+        <v>17000</v>
       </c>
       <c r="E307">
-        <v>7581</v>
+        <v>7761</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5742,10 +5742,10 @@
         <v>41</v>
       </c>
       <c r="D308">
-        <v>157307</v>
+        <v>163424</v>
       </c>
       <c r="E308">
-        <v>56470</v>
+        <v>57801</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -5759,10 +5759,10 @@
         <v>41</v>
       </c>
       <c r="D309">
-        <v>373787</v>
+        <v>378457</v>
       </c>
       <c r="E309">
-        <v>95267</v>
+        <v>96041</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5776,10 +5776,10 @@
         <v>41</v>
       </c>
       <c r="D310">
-        <v>284596</v>
+        <v>293960</v>
       </c>
       <c r="E310">
-        <v>102624</v>
+        <v>104542</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -5793,10 +5793,10 @@
         <v>41</v>
       </c>
       <c r="D311">
-        <v>449797</v>
+        <v>466342</v>
       </c>
       <c r="E311">
-        <v>141881</v>
+        <v>144810</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -5810,10 +5810,10 @@
         <v>41</v>
       </c>
       <c r="D312">
-        <v>21512</v>
+        <v>22317</v>
       </c>
       <c r="E312">
-        <v>6598</v>
+        <v>6723</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5827,10 +5827,10 @@
         <v>41</v>
       </c>
       <c r="D313">
-        <v>282174</v>
+        <v>295087</v>
       </c>
       <c r="E313">
-        <v>110508</v>
+        <v>113430</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5844,10 +5844,10 @@
         <v>41</v>
       </c>
       <c r="D314">
-        <v>49041</v>
+        <v>50275</v>
       </c>
       <c r="E314">
-        <v>22536</v>
+        <v>22838</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5861,10 +5861,10 @@
         <v>41</v>
       </c>
       <c r="D315">
-        <v>34882</v>
+        <v>35959</v>
       </c>
       <c r="E315">
-        <v>10590</v>
+        <v>10771</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -5878,10 +5878,10 @@
         <v>41</v>
       </c>
       <c r="D316">
-        <v>23721</v>
+        <v>24682</v>
       </c>
       <c r="E316">
-        <v>10819</v>
+        <v>11124</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5895,10 +5895,10 @@
         <v>41</v>
       </c>
       <c r="D317">
-        <v>757427</v>
+        <v>782839</v>
       </c>
       <c r="E317">
-        <v>219181</v>
+        <v>223359</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5912,10 +5912,10 @@
         <v>41</v>
       </c>
       <c r="D318">
-        <v>22690</v>
+        <v>23645</v>
       </c>
       <c r="E318">
-        <v>7590</v>
+        <v>7785</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5929,10 +5929,10 @@
         <v>41</v>
       </c>
       <c r="D319">
-        <v>221788</v>
+        <v>229989</v>
       </c>
       <c r="E319">
-        <v>70833</v>
+        <v>72416</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -5946,10 +5946,10 @@
         <v>41</v>
       </c>
       <c r="D320">
-        <v>246670</v>
+        <v>255557</v>
       </c>
       <c r="E320">
-        <v>89164</v>
+        <v>91231</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -5963,10 +5963,10 @@
         <v>41</v>
       </c>
       <c r="D321">
-        <v>620113</v>
+        <v>638055</v>
       </c>
       <c r="E321">
-        <v>197510</v>
+        <v>201069</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -5980,10 +5980,10 @@
         <v>41</v>
       </c>
       <c r="D322">
-        <v>235960</v>
+        <v>244890</v>
       </c>
       <c r="E322">
-        <v>78974</v>
+        <v>80903</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -5997,10 +5997,10 @@
         <v>41</v>
       </c>
       <c r="D323">
-        <v>232185</v>
+        <v>238169</v>
       </c>
       <c r="E323">
-        <v>62683</v>
+        <v>63694</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -6014,10 +6014,10 @@
         <v>41</v>
       </c>
       <c r="D324">
-        <v>238373</v>
+        <v>247931</v>
       </c>
       <c r="E324">
-        <v>88516</v>
+        <v>90418</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -6031,10 +6031,10 @@
         <v>41</v>
       </c>
       <c r="D325">
-        <v>23139</v>
+        <v>24357</v>
       </c>
       <c r="E325">
-        <v>10492</v>
+        <v>10873</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -6048,10 +6048,10 @@
         <v>41</v>
       </c>
       <c r="D326">
-        <v>174829</v>
+        <v>181766</v>
       </c>
       <c r="E326">
-        <v>51044</v>
+        <v>52360</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -6065,10 +6065,10 @@
         <v>41</v>
       </c>
       <c r="D327">
-        <v>152589</v>
+        <v>157624</v>
       </c>
       <c r="E327">
-        <v>56487</v>
+        <v>57610</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -6082,10 +6082,10 @@
         <v>41</v>
       </c>
       <c r="D328">
-        <v>359441</v>
+        <v>371582</v>
       </c>
       <c r="E328">
-        <v>104035</v>
+        <v>105909</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -6609,10 +6609,10 @@
         <v>43</v>
       </c>
       <c r="D359">
-        <v>32738</v>
+        <v>33957</v>
       </c>
       <c r="E359">
-        <v>13155</v>
+        <v>13494</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6626,10 +6626,10 @@
         <v>43</v>
       </c>
       <c r="D360">
-        <v>168120</v>
+        <v>172216</v>
       </c>
       <c r="E360">
-        <v>65402</v>
+        <v>66564</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6643,10 +6643,10 @@
         <v>43</v>
       </c>
       <c r="D361">
-        <v>3938</v>
+        <v>3975</v>
       </c>
       <c r="E361">
-        <v>2192</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -6660,10 +6660,10 @@
         <v>43</v>
       </c>
       <c r="D362">
-        <v>1404</v>
+        <v>1451</v>
       </c>
       <c r="E362">
-        <v>615</v>
+        <v>631</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6677,10 +6677,10 @@
         <v>43</v>
       </c>
       <c r="D363">
-        <v>8511</v>
+        <v>8791</v>
       </c>
       <c r="E363">
-        <v>4394</v>
+        <v>4505</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6694,10 +6694,10 @@
         <v>43</v>
       </c>
       <c r="D364">
-        <v>2516</v>
+        <v>2594</v>
       </c>
       <c r="E364">
-        <v>871</v>
+        <v>898</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6711,10 +6711,10 @@
         <v>43</v>
       </c>
       <c r="D365">
-        <v>44723</v>
+        <v>46384</v>
       </c>
       <c r="E365">
-        <v>16533</v>
+        <v>16947</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6728,10 +6728,10 @@
         <v>43</v>
       </c>
       <c r="D366">
-        <v>19551</v>
+        <v>20230</v>
       </c>
       <c r="E366">
-        <v>8047</v>
+        <v>8159</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6745,10 +6745,10 @@
         <v>43</v>
       </c>
       <c r="D367">
-        <v>57275</v>
+        <v>60053</v>
       </c>
       <c r="E367">
-        <v>18078</v>
+        <v>18709</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6762,10 +6762,10 @@
         <v>43</v>
       </c>
       <c r="D368">
-        <v>17875</v>
+        <v>18646</v>
       </c>
       <c r="E368">
-        <v>7532</v>
+        <v>7717</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6779,10 +6779,10 @@
         <v>43</v>
       </c>
       <c r="D369">
-        <v>25641</v>
+        <v>26712</v>
       </c>
       <c r="E369">
-        <v>12683</v>
+        <v>13089</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6796,10 +6796,10 @@
         <v>43</v>
       </c>
       <c r="D370">
-        <v>1028</v>
+        <v>1082</v>
       </c>
       <c r="E370">
-        <v>558</v>
+        <v>580</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -6813,10 +6813,10 @@
         <v>43</v>
       </c>
       <c r="D371">
-        <v>11947</v>
+        <v>12323</v>
       </c>
       <c r="E371">
-        <v>6111</v>
+        <v>6265</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -6830,10 +6830,10 @@
         <v>43</v>
       </c>
       <c r="D372">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E372">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6847,10 +6847,10 @@
         <v>43</v>
       </c>
       <c r="D373">
-        <v>2949</v>
+        <v>3033</v>
       </c>
       <c r="E373">
-        <v>1215</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -6864,10 +6864,10 @@
         <v>43</v>
       </c>
       <c r="D374">
-        <v>1317</v>
+        <v>1366</v>
       </c>
       <c r="E374">
-        <v>733</v>
+        <v>749</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -6881,10 +6881,10 @@
         <v>43</v>
       </c>
       <c r="D375">
-        <v>101841</v>
+        <v>104882</v>
       </c>
       <c r="E375">
-        <v>37347</v>
+        <v>38428</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6898,10 +6898,10 @@
         <v>43</v>
       </c>
       <c r="D376">
-        <v>9479</v>
+        <v>9963</v>
       </c>
       <c r="E376">
-        <v>2482</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6915,10 +6915,10 @@
         <v>43</v>
       </c>
       <c r="D377">
-        <v>18875</v>
+        <v>19276</v>
       </c>
       <c r="E377">
-        <v>7417</v>
+        <v>7565</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6932,10 +6932,10 @@
         <v>43</v>
       </c>
       <c r="D378">
-        <v>52572</v>
+        <v>54516</v>
       </c>
       <c r="E378">
-        <v>23644</v>
+        <v>24220</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -6949,10 +6949,10 @@
         <v>43</v>
       </c>
       <c r="D379">
-        <v>38232</v>
+        <v>39915</v>
       </c>
       <c r="E379">
-        <v>18051</v>
+        <v>18669</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -6966,10 +6966,10 @@
         <v>43</v>
       </c>
       <c r="D380">
-        <v>33316</v>
+        <v>34631</v>
       </c>
       <c r="E380">
-        <v>12189</v>
+        <v>12486</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -6983,10 +6983,10 @@
         <v>43</v>
       </c>
       <c r="D381">
-        <v>85586</v>
+        <v>86108</v>
       </c>
       <c r="E381">
-        <v>28588</v>
+        <v>28787</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -7000,10 +7000,10 @@
         <v>43</v>
       </c>
       <c r="D382">
-        <v>9003</v>
+        <v>9484</v>
       </c>
       <c r="E382">
-        <v>4386</v>
+        <v>4573</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -7017,10 +7017,10 @@
         <v>43</v>
       </c>
       <c r="D383">
-        <v>7760</v>
+        <v>8101</v>
       </c>
       <c r="E383">
-        <v>3191</v>
+        <v>3284</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -7034,10 +7034,10 @@
         <v>43</v>
       </c>
       <c r="D384">
-        <v>27234</v>
+        <v>28288</v>
       </c>
       <c r="E384">
-        <v>10257</v>
+        <v>10480</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -7051,10 +7051,10 @@
         <v>43</v>
       </c>
       <c r="D385">
-        <v>13839</v>
+        <v>14482</v>
       </c>
       <c r="E385">
-        <v>5820</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -7068,10 +7068,10 @@
         <v>43</v>
       </c>
       <c r="D386">
-        <v>20469</v>
+        <v>21103</v>
       </c>
       <c r="E386">
-        <v>8136</v>
+        <v>8354</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -7085,10 +7085,10 @@
         <v>44</v>
       </c>
       <c r="D387">
-        <v>285378</v>
+        <v>296234</v>
       </c>
       <c r="E387">
-        <v>104908</v>
+        <v>107099</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -7102,10 +7102,10 @@
         <v>44</v>
       </c>
       <c r="D388">
-        <v>858254</v>
+        <v>895826</v>
       </c>
       <c r="E388">
-        <v>321814</v>
+        <v>332951</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -7119,10 +7119,10 @@
         <v>44</v>
       </c>
       <c r="D389">
-        <v>82336</v>
+        <v>86002</v>
       </c>
       <c r="E389">
-        <v>25903</v>
+        <v>26579</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -7136,10 +7136,10 @@
         <v>44</v>
       </c>
       <c r="D390">
-        <v>7344</v>
+        <v>8103</v>
       </c>
       <c r="E390">
-        <v>3750</v>
+        <v>3949</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7153,10 +7153,10 @@
         <v>44</v>
       </c>
       <c r="D391">
-        <v>14539</v>
+        <v>14871</v>
       </c>
       <c r="E391">
-        <v>6008</v>
+        <v>6095</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -7170,10 +7170,10 @@
         <v>44</v>
       </c>
       <c r="D392">
-        <v>17165</v>
+        <v>18530</v>
       </c>
       <c r="E392">
-        <v>7649</v>
+        <v>8032</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7187,10 +7187,10 @@
         <v>44</v>
       </c>
       <c r="D393">
-        <v>75851</v>
+        <v>78545</v>
       </c>
       <c r="E393">
-        <v>25114</v>
+        <v>25657</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7204,10 +7204,10 @@
         <v>44</v>
       </c>
       <c r="D394">
-        <v>54103</v>
+        <v>55817</v>
       </c>
       <c r="E394">
-        <v>24003</v>
+        <v>24494</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7221,10 +7221,10 @@
         <v>44</v>
       </c>
       <c r="D395">
-        <v>289101</v>
+        <v>301316</v>
       </c>
       <c r="E395">
-        <v>97522</v>
+        <v>99742</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7238,10 +7238,10 @@
         <v>44</v>
       </c>
       <c r="D396">
-        <v>4898</v>
+        <v>5110</v>
       </c>
       <c r="E396">
-        <v>2157</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7255,10 +7255,10 @@
         <v>44</v>
       </c>
       <c r="D397">
-        <v>16550</v>
+        <v>17000</v>
       </c>
       <c r="E397">
-        <v>7581</v>
+        <v>7761</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7272,10 +7272,10 @@
         <v>44</v>
       </c>
       <c r="D398">
-        <v>137756</v>
+        <v>143194</v>
       </c>
       <c r="E398">
-        <v>52381</v>
+        <v>53674</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7289,10 +7289,10 @@
         <v>44</v>
       </c>
       <c r="D399">
-        <v>316512</v>
+        <v>318404</v>
       </c>
       <c r="E399">
-        <v>84716</v>
+        <v>85150</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -7306,10 +7306,10 @@
         <v>44</v>
       </c>
       <c r="D400">
-        <v>266721</v>
+        <v>275314</v>
       </c>
       <c r="E400">
-        <v>99209</v>
+        <v>101097</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7323,10 +7323,10 @@
         <v>44</v>
       </c>
       <c r="D401">
-        <v>424156</v>
+        <v>439630</v>
       </c>
       <c r="E401">
-        <v>135869</v>
+        <v>138647</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7340,10 +7340,10 @@
         <v>44</v>
       </c>
       <c r="D402">
-        <v>20484</v>
+        <v>21235</v>
       </c>
       <c r="E402">
-        <v>6505</v>
+        <v>6626</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7357,10 +7357,10 @@
         <v>44</v>
       </c>
       <c r="D403">
-        <v>270227</v>
+        <v>282764</v>
       </c>
       <c r="E403">
-        <v>108336</v>
+        <v>111255</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7374,10 +7374,10 @@
         <v>44</v>
       </c>
       <c r="D404">
-        <v>48913</v>
+        <v>50144</v>
       </c>
       <c r="E404">
-        <v>22494</v>
+        <v>22796</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7391,10 +7391,10 @@
         <v>44</v>
       </c>
       <c r="D405">
-        <v>31933</v>
+        <v>32926</v>
       </c>
       <c r="E405">
-        <v>10349</v>
+        <v>10525</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7408,10 +7408,10 @@
         <v>44</v>
       </c>
       <c r="D406">
-        <v>22404</v>
+        <v>23316</v>
       </c>
       <c r="E406">
-        <v>10489</v>
+        <v>10788</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7425,10 +7425,10 @@
         <v>44</v>
       </c>
       <c r="D407">
-        <v>655586</v>
+        <v>677957</v>
       </c>
       <c r="E407">
-        <v>204107</v>
+        <v>208087</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -7442,10 +7442,10 @@
         <v>44</v>
       </c>
       <c r="D408">
-        <v>13211</v>
+        <v>13682</v>
       </c>
       <c r="E408">
-        <v>6036</v>
+        <v>6177</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7459,10 +7459,10 @@
         <v>44</v>
       </c>
       <c r="D409">
-        <v>202913</v>
+        <v>210713</v>
       </c>
       <c r="E409">
-        <v>68192</v>
+        <v>69757</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7476,10 +7476,10 @@
         <v>44</v>
       </c>
       <c r="D410">
-        <v>194098</v>
+        <v>201041</v>
       </c>
       <c r="E410">
-        <v>76717</v>
+        <v>78569</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -7493,10 +7493,10 @@
         <v>44</v>
       </c>
       <c r="D411">
-        <v>581881</v>
+        <v>598140</v>
       </c>
       <c r="E411">
-        <v>191330</v>
+        <v>194742</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7510,10 +7510,10 @@
         <v>44</v>
       </c>
       <c r="D412">
-        <v>202644</v>
+        <v>210259</v>
       </c>
       <c r="E412">
-        <v>72570</v>
+        <v>74410</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -7527,10 +7527,10 @@
         <v>44</v>
       </c>
       <c r="D413">
-        <v>146599</v>
+        <v>152061</v>
       </c>
       <c r="E413">
-        <v>46261</v>
+        <v>47267</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -7544,10 +7544,10 @@
         <v>44</v>
       </c>
       <c r="D414">
-        <v>229370</v>
+        <v>238447</v>
       </c>
       <c r="E414">
-        <v>86307</v>
+        <v>88126</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7561,10 +7561,10 @@
         <v>44</v>
       </c>
       <c r="D415">
-        <v>15379</v>
+        <v>16256</v>
       </c>
       <c r="E415">
-        <v>7957</v>
+        <v>8296</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -7578,10 +7578,10 @@
         <v>44</v>
       </c>
       <c r="D416">
-        <v>147595</v>
+        <v>153478</v>
       </c>
       <c r="E416">
-        <v>47417</v>
+        <v>48717</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7595,10 +7595,10 @@
         <v>44</v>
       </c>
       <c r="D417">
-        <v>138750</v>
+        <v>143142</v>
       </c>
       <c r="E417">
-        <v>54491</v>
+        <v>55523</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7612,10 +7612,10 @@
         <v>44</v>
       </c>
       <c r="D418">
-        <v>338972</v>
+        <v>350479</v>
       </c>
       <c r="E418">
-        <v>100425</v>
+        <v>102242</v>
       </c>
     </row>
     <row r="419" spans="1:5">
